--- a/Excel final/滾算後記錄.xlsx
+++ b/Excel final/滾算後記錄.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\信邦\ai_agent2\Excel final\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E189D40C-6ED0-43E6-B5AB-6CF13A38E6A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5662B9E5-03EF-454C-9DF0-AF5B0D2230D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13695" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="滾算紀錄單(總紀錄)" sheetId="7" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="97">
   <si>
     <t>-</t>
   </si>
@@ -298,21 +298,6 @@
   </si>
   <si>
     <t>累計現金流</t>
-  </si>
-  <si>
-    <t>Discounted cash flow</t>
-  </si>
-  <si>
-    <t>Minus : Depreciation</t>
-  </si>
-  <si>
-    <t>Plus : Principle payment</t>
-  </si>
-  <si>
-    <t>Profit</t>
-  </si>
-  <si>
-    <t>EPS</t>
   </si>
   <si>
     <t>回收年限評估</t>
@@ -1056,15 +1041,15 @@
   </si>
   <si>
     <t>專案法IRR</t>
-    <phoneticPr fontId="26" type="noConversion"/>
+    <phoneticPr fontId="24" type="noConversion"/>
   </si>
   <si>
     <t>稅前淨利</t>
-    <phoneticPr fontId="26" type="noConversion"/>
+    <phoneticPr fontId="24" type="noConversion"/>
   </si>
   <si>
     <t>稅後淨利</t>
-    <phoneticPr fontId="26" type="noConversion"/>
+    <phoneticPr fontId="24" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1088,7 +1073,7 @@
       </rPr>
       <t>折舊</t>
     </r>
-    <phoneticPr fontId="26" type="noConversion"/>
+    <phoneticPr fontId="24" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1103,7 +1088,7 @@
     <numFmt numFmtId="179" formatCode="0.0000%"/>
     <numFmt numFmtId="180" formatCode="0.00000%"/>
   </numFmts>
-  <fonts count="34">
+  <fonts count="32">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1216,20 +1201,6 @@
       <b/>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FF993366"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -1401,7 +1372,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="40">
+  <borders count="38">
     <border>
       <left/>
       <right/>
@@ -1471,21 +1442,6 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
@@ -1774,19 +1730,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FFC6C6C6"/>
       </left>
@@ -1909,37 +1852,37 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="33" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="31" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="33" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="31" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="148">
+  <cellXfs count="133">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="22" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="20" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="176" fontId="22" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="20" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="22" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="20" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="176" fontId="22" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="20" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="22" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="20" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="176" fontId="22" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="20" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1958,19 +1901,19 @@
     <xf numFmtId="176" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="176" fontId="22" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="20" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="176" fontId="22" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="20" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="176" fontId="22" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="20" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="176" fontId="9" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="9" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="176" fontId="22" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="20" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="176" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1982,31 +1925,31 @@
     <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="11" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="176" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="176" fontId="12" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="12" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="176" fontId="10" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="10" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="176" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2015,31 +1958,31 @@
     <xf numFmtId="176" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="176" fontId="20" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="18" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="17" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="26" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="8" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="176" fontId="17" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="28" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="8" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="17" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="176" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="176" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2048,10 +1991,10 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2063,10 +2006,10 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2075,77 +2018,77 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="177" fontId="8" fillId="9" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="177" fontId="10" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="10" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="10" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="177" fontId="8" fillId="9" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="177" fontId="10" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="10" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="177" fontId="10" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="177" fontId="8" fillId="9" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="177" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="10" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="10" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="10" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="8" fillId="9" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="8" fillId="3" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="177" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="10" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="10" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="8" fillId="3" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="177" fontId="10" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="10" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="177" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="177" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="177" fontId="14" fillId="3" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="14" fillId="3" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="177" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="27" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="25" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="177" fontId="17" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="17" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="15" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="15" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="177" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2154,79 +2097,34 @@
     <xf numFmtId="177" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="177" fontId="16" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="16" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="177" fontId="17" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="177" fontId="18" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="17" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="177" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="8" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="18" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="17" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="15" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="19" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="17" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="17" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="20" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="17" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="15" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="177" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="17" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="17" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="177" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2247,22 +2145,22 @@
     <xf numFmtId="177" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="177" fontId="9" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="9" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="177" fontId="9" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="9" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="177" fontId="9" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="9" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="9" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="9" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="177" fontId="9" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="9" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="177" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="177" fontId="9" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2271,89 +2169,89 @@
     <xf numFmtId="177" fontId="9" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="177" fontId="9" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="9" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="9" fillId="6" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="9" fillId="6" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="9" fillId="2" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="9" fillId="2" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="179" fontId="9" fillId="2" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="9" fillId="2" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="180" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="176" fontId="21" fillId="12" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="9" fillId="11" borderId="16" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="9" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="44" fontId="9" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="176" fontId="20" fillId="13" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="20" fillId="13" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="20" fillId="13" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="20" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="176" fontId="20" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="176" fontId="20" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="176" fontId="20" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="176" fontId="20" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="20" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="20" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="176" fontId="21" fillId="12" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="21" fillId="12" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="176" fontId="21" fillId="12" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="21" fillId="12" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="19" fillId="12" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="23" fillId="12" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="19" fillId="12" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="23" fillId="12" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="19" fillId="12" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="23" fillId="12" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="20" fillId="5" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="22" fillId="5" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="20" fillId="5" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="22" fillId="5" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="20" fillId="5" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="22" fillId="5" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="22" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="176" fontId="22" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="176" fontId="22" fillId="13" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="22" fillId="13" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="22" fillId="13" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="22" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="176" fontId="22" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="176" fontId="22" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="22" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="22" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="44" fontId="9" fillId="11" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="9" fillId="0" borderId="16" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="44" fontId="9" fillId="0" borderId="16" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2663,7 +2561,7 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:H30"/>
-  <sheetFormatPr defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="10.28515625" bestFit="1" customWidth="1"/>
@@ -2676,28 +2574,28 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18.75" customHeight="1">
       <c r="A1" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>92</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="18.75" customHeight="1">
@@ -2991,7 +2889,7 @@
       <c r="H30" s="1"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="26" type="noConversion"/>
+  <phoneticPr fontId="24" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3002,7 +2900,7 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:H30"/>
-  <sheetFormatPr defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="10.28515625" bestFit="1" customWidth="1"/>
@@ -3015,28 +2913,28 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18.75" customHeight="1">
       <c r="A1" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>92</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="18.75" customHeight="1">
@@ -3330,7 +3228,7 @@
       <c r="H30" s="1"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="26" type="noConversion"/>
+  <phoneticPr fontId="24" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3340,8 +3238,8 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="B1:AJ117"/>
-  <sheetFormatPr defaultRowHeight="15.75"/>
+  <dimension ref="B1:AJ112"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="0.5703125" style="12" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="33.140625" style="12" bestFit="1" customWidth="1"/>
@@ -3360,16 +3258,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:5" ht="22.5" customHeight="1">
-      <c r="B1" s="125" t="s">
-        <v>45</v>
-      </c>
-      <c r="C1" s="126"/>
-      <c r="D1" s="126"/>
-      <c r="E1" s="127"/>
+      <c r="B1" s="127" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1" s="128"/>
+      <c r="D1" s="128"/>
+      <c r="E1" s="129"/>
     </row>
     <row r="2" spans="2:5" ht="21.75" customHeight="1">
       <c r="B2" s="13" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="4" t="s">
@@ -3381,7 +3279,7 @@
     </row>
     <row r="3" spans="2:5" ht="21.75" customHeight="1">
       <c r="B3" s="14" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C3" s="5"/>
       <c r="D3" s="6" t="s">
@@ -3393,7 +3291,7 @@
     </row>
     <row r="4" spans="2:5" ht="21.75" customHeight="1">
       <c r="B4" s="14" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C4" s="5"/>
       <c r="D4" s="6" t="s">
@@ -3405,11 +3303,11 @@
     </row>
     <row r="5" spans="2:5" ht="22.5" customHeight="1">
       <c r="B5" s="5" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C5" s="5"/>
       <c r="D5" s="5" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E5" s="5"/>
     </row>
@@ -3420,123 +3318,123 @@
       <c r="E6" s="15"/>
     </row>
     <row r="7" spans="2:5" ht="22.5" customHeight="1">
-      <c r="B7" s="128" t="s">
-        <v>51</v>
-      </c>
-      <c r="C7" s="129"/>
-      <c r="D7" s="129"/>
-      <c r="E7" s="130"/>
+      <c r="B7" s="124" t="s">
+        <v>46</v>
+      </c>
+      <c r="C7" s="125"/>
+      <c r="D7" s="125"/>
+      <c r="E7" s="126"/>
     </row>
     <row r="8" spans="2:5" ht="22.5" customHeight="1">
-      <c r="B8" s="131" t="s">
-        <v>52</v>
-      </c>
-      <c r="C8" s="132"/>
-      <c r="D8" s="132"/>
-      <c r="E8" s="133"/>
+      <c r="B8" s="130" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8" s="131"/>
+      <c r="D8" s="131"/>
+      <c r="E8" s="132"/>
     </row>
     <row r="9" spans="2:5" ht="22.5" customHeight="1">
       <c r="B9" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="C9" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="D9" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="E9" s="18" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" ht="21.75" customHeight="1">
+      <c r="B10" s="117" t="s">
+        <v>52</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C9" s="17" t="s">
+      <c r="D10" s="3"/>
+      <c r="E10" s="117"/>
+    </row>
+    <row r="11" spans="2:5" ht="21.75" customHeight="1">
+      <c r="B11" s="118"/>
+      <c r="C11" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D9" s="17" t="s">
+      <c r="D11" s="5"/>
+      <c r="E11" s="118"/>
+    </row>
+    <row r="12" spans="2:5" ht="21.75" customHeight="1">
+      <c r="B12" s="118"/>
+      <c r="C12" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="E9" s="18" t="s">
+      <c r="D12" s="5"/>
+      <c r="E12" s="118"/>
+    </row>
+    <row r="13" spans="2:5" ht="22.5" customHeight="1">
+      <c r="B13" s="118"/>
+      <c r="C13" s="7" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="10" spans="2:5" ht="21.75" customHeight="1">
-      <c r="B10" s="134" t="s">
+      <c r="D13" s="7"/>
+      <c r="E13" s="118"/>
+    </row>
+    <row r="14" spans="2:5" ht="22.5" customHeight="1">
+      <c r="B14" s="114" t="s">
         <v>57</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D10" s="3"/>
-      <c r="E10" s="134"/>
-    </row>
-    <row r="11" spans="2:5" ht="21.75" customHeight="1">
-      <c r="B11" s="135"/>
-      <c r="C11" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="D11" s="5"/>
-      <c r="E11" s="135"/>
-    </row>
-    <row r="12" spans="2:5" ht="21.75" customHeight="1">
-      <c r="B12" s="135"/>
-      <c r="C12" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="D12" s="5"/>
-      <c r="E12" s="135"/>
-    </row>
-    <row r="13" spans="2:5" ht="22.5" customHeight="1">
-      <c r="B13" s="135"/>
-      <c r="C13" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="D13" s="7"/>
-      <c r="E13" s="135"/>
-    </row>
-    <row r="14" spans="2:5" ht="22.5" customHeight="1">
-      <c r="B14" s="136" t="s">
-        <v>62</v>
-      </c>
-      <c r="C14" s="137"/>
-      <c r="D14" s="137"/>
-      <c r="E14" s="138"/>
+      <c r="C14" s="115"/>
+      <c r="D14" s="115"/>
+      <c r="E14" s="116"/>
     </row>
     <row r="15" spans="2:5" ht="22.5" customHeight="1">
       <c r="B15" s="16" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="D15" s="17" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E15" s="19" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5" ht="21.75" customHeight="1">
+      <c r="B16" s="117" t="s">
+        <v>59</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="D16" s="3"/>
+      <c r="E16" s="120"/>
+    </row>
+    <row r="17" spans="2:5" ht="21.75" customHeight="1">
+      <c r="B17" s="118"/>
+      <c r="C17" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D17" s="5"/>
+      <c r="E17" s="121"/>
+    </row>
+    <row r="18" spans="2:5" ht="21.75" customHeight="1">
+      <c r="B18" s="119"/>
+      <c r="C18" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D18" s="5"/>
+      <c r="E18" s="122"/>
+    </row>
+    <row r="19" spans="2:5" ht="54" customHeight="1">
+      <c r="B19" s="123" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="16" spans="2:5" ht="21.75" customHeight="1">
-      <c r="B16" s="134" t="s">
+      <c r="C19" s="20" t="s">
         <v>64</v>
-      </c>
-      <c r="C16" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="D16" s="3"/>
-      <c r="E16" s="140"/>
-    </row>
-    <row r="17" spans="2:5" ht="21.75" customHeight="1">
-      <c r="B17" s="135"/>
-      <c r="C17" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="D17" s="5"/>
-      <c r="E17" s="141"/>
-    </row>
-    <row r="18" spans="2:5" ht="21.75" customHeight="1">
-      <c r="B18" s="139"/>
-      <c r="C18" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="D18" s="5"/>
-      <c r="E18" s="142"/>
-    </row>
-    <row r="19" spans="2:5" ht="54" customHeight="1">
-      <c r="B19" s="143" t="s">
-        <v>68</v>
-      </c>
-      <c r="C19" s="20" t="s">
-        <v>69</v>
       </c>
       <c r="D19" s="5"/>
       <c r="E19" s="4" t="s">
@@ -3544,17 +3442,17 @@
       </c>
     </row>
     <row r="20" spans="2:5" ht="20.25" customHeight="1">
-      <c r="B20" s="135"/>
+      <c r="B20" s="118"/>
       <c r="C20" s="21" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="D20" s="5"/>
       <c r="E20" s="4"/>
     </row>
     <row r="21" spans="2:5" ht="21.75" customHeight="1">
-      <c r="B21" s="139"/>
+      <c r="B21" s="119"/>
       <c r="C21" s="5" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="6" t="s">
@@ -3563,40 +3461,40 @@
     </row>
     <row r="22" spans="2:5" ht="21.75" customHeight="1">
       <c r="B22" s="5" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="D22" s="5"/>
       <c r="E22" s="6"/>
     </row>
     <row r="23" spans="2:5" ht="21.75" customHeight="1">
       <c r="B23" s="5" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="D23" s="5"/>
       <c r="E23" s="6"/>
     </row>
     <row r="24" spans="2:5" ht="21.75" customHeight="1">
       <c r="B24" s="5" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="D24" s="5"/>
       <c r="E24" s="6"/>
     </row>
     <row r="25" spans="2:5" ht="21.75" customHeight="1">
       <c r="B25" s="5" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="D25" s="8"/>
       <c r="E25" s="6" t="s">
@@ -3605,10 +3503,10 @@
     </row>
     <row r="26" spans="2:5" ht="22.5" customHeight="1">
       <c r="B26" s="5" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="D26" s="5"/>
       <c r="E26" s="6" t="s">
@@ -3628,61 +3526,61 @@
       <c r="E28" s="15"/>
     </row>
     <row r="29" spans="2:5" ht="22.5" customHeight="1">
-      <c r="B29" s="128" t="s">
-        <v>82</v>
-      </c>
-      <c r="C29" s="129"/>
-      <c r="D29" s="130"/>
+      <c r="B29" s="124" t="s">
+        <v>77</v>
+      </c>
+      <c r="C29" s="125"/>
+      <c r="D29" s="126"/>
       <c r="E29" s="15"/>
     </row>
     <row r="30" spans="2:5" ht="22.5" customHeight="1">
       <c r="B30" s="16" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C30" s="17" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="D30" s="19" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E30" s="15"/>
     </row>
     <row r="31" spans="2:5" ht="18.75" customHeight="1">
       <c r="B31" s="13" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="D31" s="3"/>
       <c r="E31" s="15"/>
     </row>
     <row r="32" spans="2:5" ht="18.75" customHeight="1">
       <c r="B32" s="3" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="D32" s="3"/>
       <c r="E32" s="15"/>
     </row>
     <row r="33" spans="2:24" ht="18.75" customHeight="1">
       <c r="B33" s="5" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D33" s="5"/>
       <c r="E33" s="15"/>
     </row>
     <row r="34" spans="2:24" ht="18.75" customHeight="1">
       <c r="B34" s="5" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="D34" s="5"/>
       <c r="E34" s="15"/>
@@ -4407,11 +4305,11 @@
       </c>
       <c r="C54" s="71"/>
       <c r="D54" s="63" t="e">
-        <f>-(D69+D72+D73+D76+D77+D78+D79)*0.2</f>
+        <f>-(D64+D67+D68+D71+D72+D73+D74)*0.2</f>
         <v>#DIV/0!</v>
       </c>
       <c r="E54" s="63" t="e">
-        <f t="shared" ref="E54:W54" si="1">-(E69+E72+E73+E76+E77+E78+E79)*0.2</f>
+        <f t="shared" ref="E54:W54" si="1">-(E64+E67+E68+E71+E72+E73+E74)*0.2</f>
         <v>#DIV/0!</v>
       </c>
       <c r="F54" s="63" t="e">
@@ -4691,34 +4589,95 @@
       <c r="AI56" s="79"/>
       <c r="AJ56" s="79"/>
     </row>
-    <row r="57" spans="2:36" s="60" customFormat="1" ht="18.75" hidden="1" customHeight="1">
-      <c r="B57" s="83" t="s">
+    <row r="57" spans="2:36" s="60" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
+      <c r="B57" s="84" t="s">
         <v>21</v>
       </c>
-      <c r="C57" s="84">
-        <v>-37721416.399999999</v>
-      </c>
-      <c r="D57" s="85"/>
-      <c r="E57" s="85"/>
-      <c r="F57" s="86"/>
-      <c r="G57" s="86"/>
-      <c r="H57" s="86"/>
-      <c r="I57" s="86"/>
-      <c r="J57" s="86"/>
-      <c r="K57" s="86"/>
-      <c r="L57" s="86"/>
-      <c r="M57" s="86"/>
-      <c r="N57" s="86"/>
-      <c r="O57" s="86"/>
-      <c r="P57" s="86"/>
-      <c r="Q57" s="86"/>
-      <c r="R57" s="86"/>
-      <c r="S57" s="86"/>
-      <c r="T57" s="86"/>
-      <c r="U57" s="86"/>
-      <c r="V57" s="86"/>
-      <c r="W57" s="86"/>
-      <c r="X57" s="87"/>
+      <c r="C57" s="85"/>
+      <c r="D57" s="86" t="e">
+        <f>IF((D56)&gt;0,"回收","未回收")</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E57" s="86" t="e">
+        <f>IF((E56)&gt;0,"回收","未回收")</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F57" s="86" t="e">
+        <f>IF((F56)&gt;0,"回收","未回收")</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G57" s="86" t="e">
+        <f>IF((G56)&gt;0,"回收","未回收")</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H57" s="86" t="e">
+        <f>IF((H56)&gt;0,"回收","未回收")</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I57" s="86" t="e">
+        <f>IF((I56)&gt;0,"回收","未回收")</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J57" s="86" t="e">
+        <f>IF((J56)&gt;0,"回收","未回收")</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K57" s="86" t="e">
+        <f>IF((K56)&gt;0,"回收","未回收")</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L57" s="86" t="e">
+        <f>IF((L56)&gt;0,"回收","未回收")</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M57" s="86" t="e">
+        <f>IF((M56)&gt;0,"回收","未回收")</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N57" s="86" t="e">
+        <f>IF((N56)&gt;0,"回收","未回收")</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O57" s="86" t="e">
+        <f>IF((O56)&gt;0,"回收","未回收")</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="P57" s="86" t="e">
+        <f>IF((P56)&gt;0,"回收","未回收")</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Q57" s="86" t="e">
+        <f>IF((Q56)&gt;0,"回收","未回收")</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R57" s="86" t="e">
+        <f>IF((R56)&gt;0,"回收","未回收")</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S57" s="86" t="e">
+        <f>IF((S56)&gt;0,"回收","未回收")</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T57" s="86" t="e">
+        <f>IF((T56)&gt;0,"回收","未回收")</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U57" s="86" t="e">
+        <f>IF((U56)&gt;0,"回收","未回收")</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V57" s="86" t="e">
+        <f>IF((V56)&gt;0,"回收","未回收")</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W57" s="86" t="e">
+        <f>IF((W56)&gt;0,"回收","未回收")</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X57" s="86" t="e">
+        <f>IF((X56)&gt;0,"回收","未回收")</f>
+        <v>#DIV/0!</v>
+      </c>
       <c r="Y57" s="79"/>
       <c r="Z57" s="79"/>
       <c r="AA57" s="79"/>
@@ -4732,721 +4691,756 @@
       <c r="AI57" s="79"/>
       <c r="AJ57" s="79"/>
     </row>
-    <row r="58" spans="2:36" s="60" customFormat="1" ht="18.75" hidden="1" customHeight="1">
-      <c r="B58" s="83" t="s">
-        <v>22</v>
-      </c>
-      <c r="C58" s="88"/>
-      <c r="D58" s="75"/>
-      <c r="E58" s="75"/>
-      <c r="F58" s="75"/>
-      <c r="G58" s="75"/>
-      <c r="H58" s="75"/>
-      <c r="I58" s="75"/>
-      <c r="J58" s="75"/>
-      <c r="K58" s="75"/>
-      <c r="L58" s="75"/>
-      <c r="M58" s="75"/>
-      <c r="N58" s="75"/>
-      <c r="O58" s="75"/>
-      <c r="P58" s="75"/>
-      <c r="Q58" s="75"/>
-      <c r="R58" s="75"/>
-      <c r="S58" s="75"/>
-      <c r="T58" s="75"/>
-      <c r="U58" s="75"/>
-      <c r="V58" s="75"/>
-      <c r="W58" s="75"/>
-      <c r="X58" s="89"/>
-      <c r="Y58" s="79"/>
-      <c r="Z58" s="79"/>
-      <c r="AA58" s="79"/>
-      <c r="AB58" s="79"/>
-      <c r="AC58" s="79"/>
-      <c r="AD58" s="79"/>
-      <c r="AE58" s="79"/>
-      <c r="AF58" s="79"/>
-      <c r="AG58" s="79"/>
-      <c r="AH58" s="79"/>
-      <c r="AI58" s="79"/>
-      <c r="AJ58" s="79"/>
-    </row>
-    <row r="59" spans="2:36" s="60" customFormat="1" ht="18.75" hidden="1" customHeight="1">
-      <c r="B59" s="83" t="s">
-        <v>23</v>
-      </c>
-      <c r="C59" s="88"/>
-      <c r="D59" s="75"/>
-      <c r="E59" s="75"/>
-      <c r="F59" s="75"/>
-      <c r="G59" s="75"/>
-      <c r="H59" s="75"/>
-      <c r="I59" s="75"/>
-      <c r="J59" s="75"/>
-      <c r="K59" s="75"/>
-      <c r="L59" s="75"/>
-      <c r="M59" s="75"/>
-      <c r="N59" s="75"/>
-      <c r="O59" s="75"/>
-      <c r="P59" s="75"/>
-      <c r="Q59" s="75"/>
-      <c r="R59" s="75"/>
-      <c r="S59" s="75"/>
-      <c r="T59" s="75"/>
-      <c r="U59" s="75"/>
-      <c r="V59" s="75"/>
-      <c r="W59" s="75"/>
-      <c r="X59" s="89"/>
-      <c r="Y59" s="79"/>
-      <c r="Z59" s="79"/>
-      <c r="AA59" s="79"/>
-      <c r="AB59" s="79"/>
-      <c r="AC59" s="79"/>
-      <c r="AD59" s="79"/>
-      <c r="AE59" s="79"/>
-      <c r="AF59" s="79"/>
-      <c r="AG59" s="79"/>
-      <c r="AH59" s="79"/>
-      <c r="AI59" s="79"/>
-      <c r="AJ59" s="79"/>
-    </row>
-    <row r="60" spans="2:36" s="60" customFormat="1" ht="18.75" hidden="1" customHeight="1">
-      <c r="B60" s="90" t="s">
-        <v>24</v>
-      </c>
-      <c r="C60" s="91"/>
-      <c r="D60" s="92"/>
-      <c r="E60" s="92"/>
-      <c r="F60" s="92"/>
-      <c r="G60" s="92"/>
-      <c r="H60" s="92"/>
-      <c r="I60" s="92"/>
-      <c r="J60" s="92"/>
-      <c r="K60" s="92"/>
-      <c r="L60" s="92"/>
-      <c r="M60" s="92"/>
-      <c r="N60" s="92"/>
-      <c r="O60" s="92"/>
-      <c r="P60" s="92"/>
-      <c r="Q60" s="92"/>
-      <c r="R60" s="92"/>
-      <c r="S60" s="92"/>
-      <c r="T60" s="92"/>
-      <c r="U60" s="92"/>
-      <c r="V60" s="92"/>
-      <c r="W60" s="92"/>
-      <c r="X60" s="93"/>
-      <c r="Y60" s="79"/>
-      <c r="Z60" s="79"/>
-      <c r="AA60" s="79"/>
-      <c r="AB60" s="79"/>
-      <c r="AC60" s="79"/>
-      <c r="AD60" s="79"/>
-      <c r="AE60" s="79"/>
-      <c r="AF60" s="79"/>
-      <c r="AG60" s="79"/>
-      <c r="AH60" s="79"/>
-      <c r="AI60" s="79"/>
-      <c r="AJ60" s="79"/>
-    </row>
-    <row r="61" spans="2:36" s="60" customFormat="1" ht="18.75" hidden="1" customHeight="1">
-      <c r="B61" s="94" t="s">
-        <v>25</v>
-      </c>
-      <c r="C61" s="95"/>
-      <c r="D61" s="96"/>
-      <c r="E61" s="96"/>
-      <c r="F61" s="97"/>
-      <c r="G61" s="97"/>
-      <c r="H61" s="97"/>
-      <c r="I61" s="97"/>
-      <c r="J61" s="97"/>
-      <c r="K61" s="97"/>
-      <c r="L61" s="97"/>
-      <c r="M61" s="97"/>
-      <c r="N61" s="97"/>
-      <c r="O61" s="97"/>
-      <c r="P61" s="97"/>
-      <c r="Q61" s="97"/>
-      <c r="R61" s="97"/>
-      <c r="S61" s="97"/>
-      <c r="T61" s="97"/>
-      <c r="U61" s="97"/>
-      <c r="V61" s="97"/>
-      <c r="W61" s="97"/>
-      <c r="X61" s="98"/>
-      <c r="Y61" s="79"/>
-      <c r="Z61" s="79"/>
-      <c r="AA61" s="79"/>
-      <c r="AB61" s="79"/>
-      <c r="AC61" s="79"/>
-      <c r="AD61" s="79"/>
-      <c r="AE61" s="79"/>
-      <c r="AF61" s="79"/>
-      <c r="AG61" s="79"/>
-      <c r="AH61" s="79"/>
-      <c r="AI61" s="79"/>
-      <c r="AJ61" s="79"/>
-    </row>
-    <row r="62" spans="2:36" s="60" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B62" s="99" t="s">
-        <v>26</v>
-      </c>
-      <c r="C62" s="100"/>
-      <c r="D62" s="101" t="e">
-        <f>IF((D56)&gt;0,"回收","未回收")</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E62" s="101" t="e">
-        <f t="shared" ref="E62:X62" si="4">IF((E56)&gt;0,"回收","未回收")</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F62" s="101" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G62" s="101" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H62" s="101" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I62" s="101" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J62" s="101" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K62" s="101" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L62" s="101" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M62" s="101" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N62" s="101" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O62" s="101" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P62" s="101" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q62" s="101" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R62" s="101" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S62" s="101" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T62" s="101" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U62" s="101" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V62" s="101" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W62" s="101" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X62" s="101" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y62" s="79"/>
-      <c r="Z62" s="79"/>
-      <c r="AA62" s="79"/>
-      <c r="AB62" s="79"/>
-      <c r="AC62" s="79"/>
-      <c r="AD62" s="79"/>
-      <c r="AE62" s="79"/>
-      <c r="AF62" s="79"/>
-      <c r="AG62" s="79"/>
-      <c r="AH62" s="79"/>
-      <c r="AI62" s="79"/>
-      <c r="AJ62" s="79"/>
-    </row>
-    <row r="63" spans="2:36" ht="18.75" customHeight="1">
-      <c r="B63" s="37" t="s">
-        <v>98</v>
-      </c>
-      <c r="C63" s="124" t="e">
+    <row r="58" spans="2:36" ht="18.75" customHeight="1">
+      <c r="B58" s="37" t="s">
+        <v>93</v>
+      </c>
+      <c r="C58" s="109" t="e">
         <f>IRR(C55:W55)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D63" s="9"/>
-      <c r="E63" s="9"/>
-      <c r="F63" s="22"/>
-      <c r="G63" s="22"/>
-      <c r="H63" s="22"/>
-      <c r="I63" s="22"/>
-      <c r="J63" s="22"/>
-      <c r="K63" s="22"/>
-      <c r="L63" s="22"/>
-      <c r="M63" s="22"/>
-      <c r="N63" s="22"/>
-      <c r="O63" s="22"/>
-      <c r="P63" s="22"/>
-      <c r="Q63" s="22"/>
-      <c r="R63" s="22"/>
-      <c r="S63" s="22"/>
-      <c r="T63" s="22"/>
-      <c r="U63" s="22"/>
-      <c r="V63" s="22"/>
-      <c r="W63" s="22"/>
-      <c r="X63" s="22"/>
-      <c r="Y63" s="32"/>
-      <c r="Z63" s="32"/>
-      <c r="AA63" s="32"/>
-      <c r="AB63" s="32"/>
-      <c r="AC63" s="32"/>
-      <c r="AD63" s="32"/>
-      <c r="AE63" s="32"/>
-      <c r="AF63" s="32"/>
-      <c r="AG63" s="32"/>
-      <c r="AH63" s="32"/>
-      <c r="AI63" s="32"/>
-      <c r="AJ63" s="32"/>
-    </row>
-    <row r="64" spans="2:36" ht="18.75" customHeight="1">
-      <c r="B64" s="22"/>
-      <c r="C64" s="9"/>
-      <c r="D64" s="9"/>
-      <c r="E64" s="9"/>
-      <c r="F64" s="22"/>
-      <c r="G64" s="22"/>
-      <c r="H64" s="22"/>
-      <c r="I64" s="22"/>
-      <c r="J64" s="22"/>
-      <c r="K64" s="22"/>
-      <c r="L64" s="22"/>
-      <c r="M64" s="9"/>
-      <c r="N64" s="22"/>
-      <c r="O64" s="22"/>
-      <c r="P64" s="22"/>
-      <c r="Q64" s="22"/>
-      <c r="R64" s="22"/>
-      <c r="S64" s="22"/>
-      <c r="T64" s="22"/>
-      <c r="U64" s="22"/>
-      <c r="V64" s="22"/>
-      <c r="W64" s="22"/>
-      <c r="X64" s="22"/>
-      <c r="Y64" s="32"/>
-      <c r="Z64" s="32"/>
-      <c r="AA64" s="32"/>
-      <c r="AB64" s="32"/>
-      <c r="AC64" s="32"/>
-      <c r="AD64" s="32"/>
-      <c r="AE64" s="32"/>
-      <c r="AF64" s="32"/>
-      <c r="AG64" s="32"/>
-      <c r="AH64" s="32"/>
-      <c r="AI64" s="32"/>
-      <c r="AJ64" s="32"/>
-    </row>
-    <row r="65" spans="2:36" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B65" s="53"/>
-      <c r="C65" s="54" t="s">
+      <c r="D58" s="9"/>
+      <c r="E58" s="9"/>
+      <c r="F58" s="22"/>
+      <c r="G58" s="22"/>
+      <c r="H58" s="22"/>
+      <c r="I58" s="22"/>
+      <c r="J58" s="22"/>
+      <c r="K58" s="22"/>
+      <c r="L58" s="22"/>
+      <c r="M58" s="22"/>
+      <c r="N58" s="22"/>
+      <c r="O58" s="22"/>
+      <c r="P58" s="22"/>
+      <c r="Q58" s="22"/>
+      <c r="R58" s="22"/>
+      <c r="S58" s="22"/>
+      <c r="T58" s="22"/>
+      <c r="U58" s="22"/>
+      <c r="V58" s="22"/>
+      <c r="W58" s="22"/>
+      <c r="X58" s="22"/>
+      <c r="Y58" s="32"/>
+      <c r="Z58" s="32"/>
+      <c r="AA58" s="32"/>
+      <c r="AB58" s="32"/>
+      <c r="AC58" s="32"/>
+      <c r="AD58" s="32"/>
+      <c r="AE58" s="32"/>
+      <c r="AF58" s="32"/>
+      <c r="AG58" s="32"/>
+      <c r="AH58" s="32"/>
+      <c r="AI58" s="32"/>
+      <c r="AJ58" s="32"/>
+    </row>
+    <row r="59" spans="2:36" ht="18.75" customHeight="1">
+      <c r="B59" s="22"/>
+      <c r="C59" s="9"/>
+      <c r="D59" s="9"/>
+      <c r="E59" s="9"/>
+      <c r="F59" s="22"/>
+      <c r="G59" s="22"/>
+      <c r="H59" s="22"/>
+      <c r="I59" s="22"/>
+      <c r="J59" s="22"/>
+      <c r="K59" s="22"/>
+      <c r="L59" s="22"/>
+      <c r="M59" s="9"/>
+      <c r="N59" s="22"/>
+      <c r="O59" s="22"/>
+      <c r="P59" s="22"/>
+      <c r="Q59" s="22"/>
+      <c r="R59" s="22"/>
+      <c r="S59" s="22"/>
+      <c r="T59" s="22"/>
+      <c r="U59" s="22"/>
+      <c r="V59" s="22"/>
+      <c r="W59" s="22"/>
+      <c r="X59" s="22"/>
+      <c r="Y59" s="32"/>
+      <c r="Z59" s="32"/>
+      <c r="AA59" s="32"/>
+      <c r="AB59" s="32"/>
+      <c r="AC59" s="32"/>
+      <c r="AD59" s="32"/>
+      <c r="AE59" s="32"/>
+      <c r="AF59" s="32"/>
+      <c r="AG59" s="32"/>
+      <c r="AH59" s="32"/>
+      <c r="AI59" s="32"/>
+      <c r="AJ59" s="32"/>
+    </row>
+    <row r="60" spans="2:36" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
+      <c r="B60" s="53"/>
+      <c r="C60" s="54" t="s">
         <v>1</v>
       </c>
-      <c r="D65" s="54">
+      <c r="D60" s="54">
         <f>D37</f>
         <v>2020</v>
       </c>
-      <c r="E65" s="54">
+      <c r="E60" s="54">
         <f>E37</f>
         <v>2021</v>
       </c>
-      <c r="F65" s="54">
-        <f t="shared" ref="F65:W65" si="5">F37</f>
+      <c r="F60" s="54">
+        <f>F37</f>
         <v>2022</v>
       </c>
-      <c r="G65" s="54">
-        <f t="shared" si="5"/>
+      <c r="G60" s="54">
+        <f>G37</f>
         <v>2023</v>
       </c>
-      <c r="H65" s="54">
-        <f t="shared" si="5"/>
+      <c r="H60" s="54">
+        <f>H37</f>
         <v>2024</v>
       </c>
-      <c r="I65" s="54">
-        <f t="shared" si="5"/>
+      <c r="I60" s="54">
+        <f>I37</f>
         <v>2025</v>
       </c>
-      <c r="J65" s="54">
-        <f t="shared" si="5"/>
+      <c r="J60" s="54">
+        <f>J37</f>
         <v>2026</v>
       </c>
-      <c r="K65" s="54">
-        <f t="shared" si="5"/>
+      <c r="K60" s="54">
+        <f>K37</f>
         <v>2027</v>
       </c>
-      <c r="L65" s="54">
-        <f t="shared" si="5"/>
+      <c r="L60" s="54">
+        <f>L37</f>
         <v>2028</v>
       </c>
-      <c r="M65" s="54">
-        <f t="shared" si="5"/>
+      <c r="M60" s="54">
+        <f>M37</f>
         <v>2029</v>
       </c>
-      <c r="N65" s="54">
-        <f t="shared" si="5"/>
+      <c r="N60" s="54">
+        <f>N37</f>
         <v>2030</v>
       </c>
-      <c r="O65" s="54">
-        <f t="shared" si="5"/>
+      <c r="O60" s="54">
+        <f>O37</f>
         <v>2031</v>
       </c>
-      <c r="P65" s="54">
-        <f t="shared" si="5"/>
+      <c r="P60" s="54">
+        <f>P37</f>
         <v>2032</v>
       </c>
-      <c r="Q65" s="54">
-        <f t="shared" si="5"/>
+      <c r="Q60" s="54">
+        <f>Q37</f>
         <v>2033</v>
       </c>
-      <c r="R65" s="54">
-        <f t="shared" si="5"/>
+      <c r="R60" s="54">
+        <f>R37</f>
         <v>2034</v>
       </c>
-      <c r="S65" s="54">
-        <f t="shared" si="5"/>
+      <c r="S60" s="54">
+        <f>S37</f>
         <v>2035</v>
       </c>
-      <c r="T65" s="54">
-        <f t="shared" si="5"/>
+      <c r="T60" s="54">
+        <f>T37</f>
         <v>2036</v>
       </c>
-      <c r="U65" s="54">
-        <f t="shared" si="5"/>
+      <c r="U60" s="54">
+        <f>U37</f>
         <v>2037</v>
       </c>
-      <c r="V65" s="54">
-        <f t="shared" si="5"/>
+      <c r="V60" s="54">
+        <f>V37</f>
         <v>2038</v>
       </c>
-      <c r="W65" s="54">
-        <f t="shared" si="5"/>
+      <c r="W60" s="54">
+        <f>W37</f>
         <v>2039</v>
       </c>
-      <c r="X65" s="54"/>
-      <c r="Y65" s="55"/>
-      <c r="Z65" s="55"/>
-      <c r="AA65" s="55"/>
-      <c r="AB65" s="55"/>
-      <c r="AC65" s="55"/>
-      <c r="AD65" s="55"/>
-      <c r="AE65" s="55"/>
-      <c r="AF65" s="55"/>
-      <c r="AG65" s="55"/>
-      <c r="AH65" s="55"/>
-      <c r="AI65" s="55"/>
-      <c r="AJ65" s="55"/>
-    </row>
-    <row r="66" spans="2:36" ht="18.75" customHeight="1">
-      <c r="B66" s="23">
-        <v>0</v>
-      </c>
-      <c r="C66" s="24"/>
-      <c r="D66" s="25"/>
-      <c r="E66" s="25"/>
-      <c r="F66" s="26"/>
-      <c r="G66" s="27"/>
-      <c r="H66" s="27"/>
-      <c r="I66" s="27"/>
-      <c r="J66" s="27"/>
-      <c r="K66" s="27"/>
-      <c r="L66" s="27"/>
-      <c r="M66" s="27"/>
-      <c r="N66" s="27"/>
-      <c r="O66" s="27"/>
-      <c r="P66" s="27"/>
-      <c r="Q66" s="27"/>
-      <c r="R66" s="27"/>
-      <c r="S66" s="27"/>
-      <c r="T66" s="38" t="s">
+      <c r="X60" s="54"/>
+      <c r="Y60" s="55"/>
+      <c r="Z60" s="55"/>
+      <c r="AA60" s="55"/>
+      <c r="AB60" s="55"/>
+      <c r="AC60" s="55"/>
+      <c r="AD60" s="55"/>
+      <c r="AE60" s="55"/>
+      <c r="AF60" s="55"/>
+      <c r="AG60" s="55"/>
+      <c r="AH60" s="55"/>
+      <c r="AI60" s="55"/>
+      <c r="AJ60" s="55"/>
+    </row>
+    <row r="61" spans="2:36" ht="18.75" customHeight="1">
+      <c r="B61" s="23">
+        <v>0</v>
+      </c>
+      <c r="C61" s="24"/>
+      <c r="D61" s="25"/>
+      <c r="E61" s="25"/>
+      <c r="F61" s="26"/>
+      <c r="G61" s="27"/>
+      <c r="H61" s="27"/>
+      <c r="I61" s="27"/>
+      <c r="J61" s="27"/>
+      <c r="K61" s="27"/>
+      <c r="L61" s="27"/>
+      <c r="M61" s="27"/>
+      <c r="N61" s="27"/>
+      <c r="O61" s="27"/>
+      <c r="P61" s="27"/>
+      <c r="Q61" s="27"/>
+      <c r="R61" s="27"/>
+      <c r="S61" s="27"/>
+      <c r="T61" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="U66" s="27"/>
-      <c r="V66" s="27"/>
-      <c r="W66" s="27"/>
-      <c r="X66" s="29"/>
-    </row>
-    <row r="67" spans="2:36" customFormat="1" ht="18.75" customHeight="1">
-      <c r="B67" s="42" t="s">
+      <c r="U61" s="27"/>
+      <c r="V61" s="27"/>
+      <c r="W61" s="27"/>
+      <c r="X61" s="29"/>
+    </row>
+    <row r="62" spans="2:36" customFormat="1" ht="18.75" customHeight="1">
+      <c r="B62" s="42" t="s">
         <v>3</v>
       </c>
-      <c r="C67" s="43">
-        <v>0</v>
-      </c>
-      <c r="D67" s="44">
+      <c r="C62" s="43">
+        <v>0</v>
+      </c>
+      <c r="D62" s="44">
         <v>1</v>
       </c>
-      <c r="E67" s="44">
+      <c r="E62" s="44">
         <v>2</v>
       </c>
-      <c r="F67" s="44">
+      <c r="F62" s="44">
         <v>3</v>
       </c>
-      <c r="G67" s="44">
+      <c r="G62" s="44">
         <v>4</v>
       </c>
-      <c r="H67" s="44">
+      <c r="H62" s="44">
         <v>5</v>
       </c>
-      <c r="I67" s="44">
+      <c r="I62" s="44">
         <v>6</v>
       </c>
-      <c r="J67" s="44">
+      <c r="J62" s="44">
         <v>7</v>
       </c>
-      <c r="K67" s="44">
+      <c r="K62" s="44">
         <v>8</v>
       </c>
-      <c r="L67" s="44">
+      <c r="L62" s="44">
         <v>9</v>
       </c>
-      <c r="M67" s="44">
+      <c r="M62" s="44">
         <v>10</v>
       </c>
-      <c r="N67" s="44">
+      <c r="N62" s="44">
         <v>11</v>
       </c>
-      <c r="O67" s="44">
+      <c r="O62" s="44">
         <v>12</v>
       </c>
-      <c r="P67" s="44">
+      <c r="P62" s="44">
         <v>13</v>
       </c>
-      <c r="Q67" s="44">
+      <c r="Q62" s="44">
         <v>14</v>
       </c>
-      <c r="R67" s="44">
+      <c r="R62" s="44">
         <v>15</v>
       </c>
-      <c r="S67" s="44">
+      <c r="S62" s="44">
         <v>16</v>
       </c>
-      <c r="T67" s="47">
+      <c r="T62" s="47">
         <v>17</v>
       </c>
-      <c r="U67" s="44">
+      <c r="U62" s="44">
         <v>18</v>
       </c>
-      <c r="V67" s="44">
+      <c r="V62" s="44">
         <v>19</v>
       </c>
-      <c r="W67" s="44">
+      <c r="W62" s="44">
         <v>20</v>
       </c>
-      <c r="X67" s="46"/>
-    </row>
-    <row r="68" spans="2:36" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B68" s="30" t="s">
+      <c r="X62" s="46"/>
+    </row>
+    <row r="63" spans="2:36" ht="18.75" customHeight="1" thickBot="1">
+      <c r="B63" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="C68" s="10">
-        <v>0</v>
-      </c>
-      <c r="D68" s="11">
+      <c r="C63" s="10">
+        <v>0</v>
+      </c>
+      <c r="D63" s="11">
         <f>D40</f>
         <v>0</v>
       </c>
-      <c r="E68" s="11">
-        <f t="shared" ref="E68:W68" si="6">E40</f>
-        <v>0</v>
-      </c>
-      <c r="F68" s="11">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="G68" s="11">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="H68" s="11">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="I68" s="11">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="J68" s="11">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="K68" s="11">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="L68" s="11">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="M68" s="11">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="N68" s="11">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="O68" s="11">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="P68" s="11">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q68" s="11">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="R68" s="11">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="S68" s="11">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="T68" s="11">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="U68" s="11">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="V68" s="11">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="W68" s="11">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="X68" s="31"/>
-    </row>
-    <row r="69" spans="2:36" s="60" customFormat="1" ht="18.75" customHeight="1">
-      <c r="B69" s="56" t="s">
+      <c r="E63" s="11">
+        <f>E40</f>
+        <v>0</v>
+      </c>
+      <c r="F63" s="11">
+        <f>F40</f>
+        <v>0</v>
+      </c>
+      <c r="G63" s="11">
+        <f>G40</f>
+        <v>0</v>
+      </c>
+      <c r="H63" s="11">
+        <f>H40</f>
+        <v>0</v>
+      </c>
+      <c r="I63" s="11">
+        <f>I40</f>
+        <v>0</v>
+      </c>
+      <c r="J63" s="11">
+        <f>J40</f>
+        <v>0</v>
+      </c>
+      <c r="K63" s="11">
+        <f>K40</f>
+        <v>0</v>
+      </c>
+      <c r="L63" s="11">
+        <f>L40</f>
+        <v>0</v>
+      </c>
+      <c r="M63" s="11">
+        <f>M40</f>
+        <v>0</v>
+      </c>
+      <c r="N63" s="11">
+        <f>N40</f>
+        <v>0</v>
+      </c>
+      <c r="O63" s="11">
+        <f>O40</f>
+        <v>0</v>
+      </c>
+      <c r="P63" s="11">
+        <f>P40</f>
+        <v>0</v>
+      </c>
+      <c r="Q63" s="11">
+        <f>Q40</f>
+        <v>0</v>
+      </c>
+      <c r="R63" s="11">
+        <f>R40</f>
+        <v>0</v>
+      </c>
+      <c r="S63" s="11">
+        <f>S40</f>
+        <v>0</v>
+      </c>
+      <c r="T63" s="11">
+        <f>T40</f>
+        <v>0</v>
+      </c>
+      <c r="U63" s="11">
+        <f>U40</f>
+        <v>0</v>
+      </c>
+      <c r="V63" s="11">
+        <f>V40</f>
+        <v>0</v>
+      </c>
+      <c r="W63" s="11">
+        <f>W40</f>
+        <v>0</v>
+      </c>
+      <c r="X63" s="31"/>
+    </row>
+    <row r="64" spans="2:36" s="60" customFormat="1" ht="18.75" customHeight="1">
+      <c r="B64" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="C69" s="57" t="s">
-        <v>0</v>
-      </c>
-      <c r="D69" s="58">
+      <c r="C64" s="57" t="s">
+        <v>0</v>
+      </c>
+      <c r="D64" s="58">
         <f>D41</f>
         <v>0</v>
       </c>
-      <c r="E69" s="58">
-        <f t="shared" ref="E69:W69" si="7">E41</f>
-        <v>0</v>
-      </c>
-      <c r="F69" s="58">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="G69" s="58">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="H69" s="58">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="I69" s="58">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J69" s="58">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="K69" s="58">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="L69" s="58">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="M69" s="58">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="N69" s="58">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="O69" s="58">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="P69" s="58">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="Q69" s="58">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="R69" s="58">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="S69" s="58">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="T69" s="58">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="U69" s="58">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="V69" s="58">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="W69" s="58">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="X69" s="59"/>
-    </row>
-    <row r="70" spans="2:36" s="60" customFormat="1" ht="18.75" customHeight="1">
-      <c r="B70" s="61" t="s">
+      <c r="E64" s="58">
+        <f>E41</f>
+        <v>0</v>
+      </c>
+      <c r="F64" s="58">
+        <f>F41</f>
+        <v>0</v>
+      </c>
+      <c r="G64" s="58">
+        <f>G41</f>
+        <v>0</v>
+      </c>
+      <c r="H64" s="58">
+        <f>H41</f>
+        <v>0</v>
+      </c>
+      <c r="I64" s="58">
+        <f>I41</f>
+        <v>0</v>
+      </c>
+      <c r="J64" s="58">
+        <f>J41</f>
+        <v>0</v>
+      </c>
+      <c r="K64" s="58">
+        <f>K41</f>
+        <v>0</v>
+      </c>
+      <c r="L64" s="58">
+        <f>L41</f>
+        <v>0</v>
+      </c>
+      <c r="M64" s="58">
+        <f>M41</f>
+        <v>0</v>
+      </c>
+      <c r="N64" s="58">
+        <f>N41</f>
+        <v>0</v>
+      </c>
+      <c r="O64" s="58">
+        <f>O41</f>
+        <v>0</v>
+      </c>
+      <c r="P64" s="58">
+        <f>P41</f>
+        <v>0</v>
+      </c>
+      <c r="Q64" s="58">
+        <f>Q41</f>
+        <v>0</v>
+      </c>
+      <c r="R64" s="58">
+        <f>R41</f>
+        <v>0</v>
+      </c>
+      <c r="S64" s="58">
+        <f>S41</f>
+        <v>0</v>
+      </c>
+      <c r="T64" s="58">
+        <f>T41</f>
+        <v>0</v>
+      </c>
+      <c r="U64" s="58">
+        <f>U41</f>
+        <v>0</v>
+      </c>
+      <c r="V64" s="58">
+        <f>V41</f>
+        <v>0</v>
+      </c>
+      <c r="W64" s="58">
+        <f>W41</f>
+        <v>0</v>
+      </c>
+      <c r="X64" s="59"/>
+    </row>
+    <row r="65" spans="2:24" s="60" customFormat="1" ht="18.75" customHeight="1">
+      <c r="B65" s="61" t="s">
         <v>6</v>
+      </c>
+      <c r="C65" s="62" t="s">
+        <v>0</v>
+      </c>
+      <c r="D65" s="63"/>
+      <c r="E65" s="63"/>
+      <c r="F65" s="63"/>
+      <c r="G65" s="63" t="s">
+        <v>0</v>
+      </c>
+      <c r="H65" s="63" t="s">
+        <v>0</v>
+      </c>
+      <c r="I65" s="63" t="s">
+        <v>0</v>
+      </c>
+      <c r="J65" s="63" t="s">
+        <v>0</v>
+      </c>
+      <c r="K65" s="63" t="s">
+        <v>0</v>
+      </c>
+      <c r="L65" s="63" t="s">
+        <v>0</v>
+      </c>
+      <c r="M65" s="63" t="s">
+        <v>0</v>
+      </c>
+      <c r="N65" s="63" t="s">
+        <v>0</v>
+      </c>
+      <c r="O65" s="63" t="s">
+        <v>0</v>
+      </c>
+      <c r="P65" s="63" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="63" t="s">
+        <v>0</v>
+      </c>
+      <c r="R65" s="63" t="s">
+        <v>0</v>
+      </c>
+      <c r="S65" s="63" t="s">
+        <v>0</v>
+      </c>
+      <c r="T65" s="63" t="s">
+        <v>0</v>
+      </c>
+      <c r="U65" s="63" t="s">
+        <v>0</v>
+      </c>
+      <c r="V65" s="63" t="s">
+        <v>0</v>
+      </c>
+      <c r="W65" s="63" t="s">
+        <v>0</v>
+      </c>
+      <c r="X65" s="64"/>
+    </row>
+    <row r="66" spans="2:24" s="60" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
+      <c r="B66" s="65" t="s">
+        <v>7</v>
+      </c>
+      <c r="C66" s="66"/>
+      <c r="D66" s="67"/>
+      <c r="E66" s="67"/>
+      <c r="F66" s="67"/>
+      <c r="G66" s="67"/>
+      <c r="H66" s="67"/>
+      <c r="I66" s="67"/>
+      <c r="J66" s="67"/>
+      <c r="K66" s="67"/>
+      <c r="L66" s="67"/>
+      <c r="M66" s="67"/>
+      <c r="N66" s="67"/>
+      <c r="O66" s="67"/>
+      <c r="P66" s="67"/>
+      <c r="Q66" s="67"/>
+      <c r="R66" s="67"/>
+      <c r="S66" s="67"/>
+      <c r="T66" s="67"/>
+      <c r="U66" s="67"/>
+      <c r="V66" s="67"/>
+      <c r="W66" s="67"/>
+      <c r="X66" s="68"/>
+    </row>
+    <row r="67" spans="2:24" s="60" customFormat="1" ht="18.75" customHeight="1">
+      <c r="B67" s="69" t="s">
+        <v>96</v>
+      </c>
+      <c r="C67" s="62"/>
+      <c r="D67" s="70" t="e">
+        <f>$C$44/$E$16</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E67" s="70" t="e">
+        <f t="shared" ref="E67:W67" si="4">$C$44/$E$16</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F67" s="70" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G67" s="70" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H67" s="70" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I67" s="70" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J67" s="70" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K67" s="70" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L67" s="70" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M67" s="70" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N67" s="70" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O67" s="70" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="P67" s="70" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Q67" s="70" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R67" s="70" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S67" s="70" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T67" s="70" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U67" s="70" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V67" s="70" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W67" s="70" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X67" s="64"/>
+    </row>
+    <row r="68" spans="2:24" s="60" customFormat="1" ht="18.75" customHeight="1">
+      <c r="B68" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="C68" s="62" t="s">
+        <v>0</v>
+      </c>
+      <c r="D68" s="63">
+        <f>D45</f>
+        <v>0</v>
+      </c>
+      <c r="E68" s="63">
+        <f>E45</f>
+        <v>0</v>
+      </c>
+      <c r="F68" s="63">
+        <f>F45</f>
+        <v>0</v>
+      </c>
+      <c r="G68" s="63">
+        <f>G45</f>
+        <v>0</v>
+      </c>
+      <c r="H68" s="63">
+        <f>H45</f>
+        <v>0</v>
+      </c>
+      <c r="I68" s="63">
+        <f>I45</f>
+        <v>0</v>
+      </c>
+      <c r="J68" s="63">
+        <f>J45</f>
+        <v>0</v>
+      </c>
+      <c r="K68" s="63">
+        <f>K45</f>
+        <v>0</v>
+      </c>
+      <c r="L68" s="63">
+        <f>L45</f>
+        <v>0</v>
+      </c>
+      <c r="M68" s="63">
+        <f>M45</f>
+        <v>0</v>
+      </c>
+      <c r="N68" s="63">
+        <f>N45</f>
+        <v>0</v>
+      </c>
+      <c r="O68" s="63">
+        <f>O45</f>
+        <v>0</v>
+      </c>
+      <c r="P68" s="63">
+        <f>P45</f>
+        <v>0</v>
+      </c>
+      <c r="Q68" s="63">
+        <f>Q45</f>
+        <v>0</v>
+      </c>
+      <c r="R68" s="63">
+        <f>R45</f>
+        <v>0</v>
+      </c>
+      <c r="S68" s="63">
+        <f>S45</f>
+        <v>0</v>
+      </c>
+      <c r="T68" s="63">
+        <f>T45</f>
+        <v>0</v>
+      </c>
+      <c r="U68" s="63">
+        <f>U45</f>
+        <v>0</v>
+      </c>
+      <c r="V68" s="63">
+        <f>V45</f>
+        <v>0</v>
+      </c>
+      <c r="W68" s="63">
+        <f>W45</f>
+        <v>0</v>
+      </c>
+      <c r="X68" s="64"/>
+    </row>
+    <row r="69" spans="2:24" s="60" customFormat="1" ht="18.75" customHeight="1">
+      <c r="B69" s="69" t="s">
+        <v>10</v>
+      </c>
+      <c r="C69" s="62"/>
+      <c r="D69" s="63"/>
+      <c r="E69" s="63"/>
+      <c r="F69" s="63"/>
+      <c r="G69" s="63"/>
+      <c r="H69" s="63"/>
+      <c r="I69" s="63"/>
+      <c r="J69" s="63"/>
+      <c r="K69" s="63"/>
+      <c r="L69" s="63"/>
+      <c r="M69" s="63"/>
+      <c r="N69" s="63"/>
+      <c r="O69" s="63"/>
+      <c r="P69" s="63"/>
+      <c r="Q69" s="63"/>
+      <c r="R69" s="63"/>
+      <c r="S69" s="63"/>
+      <c r="T69" s="63"/>
+      <c r="U69" s="63"/>
+      <c r="V69" s="63"/>
+      <c r="W69" s="63"/>
+      <c r="X69" s="64"/>
+    </row>
+    <row r="70" spans="2:24" s="60" customFormat="1" ht="18.75" customHeight="1">
+      <c r="B70" s="69" t="s">
+        <v>11</v>
       </c>
       <c r="C70" s="62" t="s">
         <v>0</v>
@@ -5454,269 +5448,297 @@
       <c r="D70" s="63"/>
       <c r="E70" s="63"/>
       <c r="F70" s="63"/>
-      <c r="G70" s="63" t="s">
-        <v>0</v>
-      </c>
-      <c r="H70" s="63" t="s">
-        <v>0</v>
-      </c>
-      <c r="I70" s="63" t="s">
-        <v>0</v>
-      </c>
-      <c r="J70" s="63" t="s">
-        <v>0</v>
-      </c>
-      <c r="K70" s="63" t="s">
-        <v>0</v>
-      </c>
-      <c r="L70" s="63" t="s">
-        <v>0</v>
-      </c>
-      <c r="M70" s="63" t="s">
-        <v>0</v>
-      </c>
-      <c r="N70" s="63" t="s">
-        <v>0</v>
-      </c>
-      <c r="O70" s="63" t="s">
-        <v>0</v>
-      </c>
-      <c r="P70" s="63" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q70" s="63" t="s">
-        <v>0</v>
-      </c>
-      <c r="R70" s="63" t="s">
-        <v>0</v>
-      </c>
-      <c r="S70" s="63" t="s">
-        <v>0</v>
-      </c>
-      <c r="T70" s="63" t="s">
-        <v>0</v>
-      </c>
-      <c r="U70" s="63" t="s">
-        <v>0</v>
-      </c>
-      <c r="V70" s="63" t="s">
-        <v>0</v>
-      </c>
-      <c r="W70" s="63" t="s">
-        <v>0</v>
-      </c>
+      <c r="G70" s="63"/>
+      <c r="H70" s="63"/>
+      <c r="I70" s="63"/>
+      <c r="J70" s="63"/>
+      <c r="K70" s="63"/>
+      <c r="L70" s="63"/>
+      <c r="M70" s="63"/>
+      <c r="N70" s="63"/>
+      <c r="O70" s="63"/>
+      <c r="P70" s="63"/>
+      <c r="Q70" s="63"/>
+      <c r="R70" s="63"/>
+      <c r="S70" s="63"/>
+      <c r="T70" s="63"/>
+      <c r="U70" s="63"/>
+      <c r="V70" s="63"/>
+      <c r="W70" s="63"/>
       <c r="X70" s="64"/>
     </row>
-    <row r="71" spans="2:36" s="60" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B71" s="65" t="s">
-        <v>7</v>
-      </c>
-      <c r="C71" s="66"/>
-      <c r="D71" s="67"/>
-      <c r="E71" s="67"/>
-      <c r="F71" s="67"/>
-      <c r="G71" s="67"/>
-      <c r="H71" s="67"/>
-      <c r="I71" s="67"/>
-      <c r="J71" s="67"/>
-      <c r="K71" s="67"/>
-      <c r="L71" s="67"/>
-      <c r="M71" s="67"/>
-      <c r="N71" s="67"/>
-      <c r="O71" s="67"/>
-      <c r="P71" s="67"/>
-      <c r="Q71" s="67"/>
-      <c r="R71" s="67"/>
-      <c r="S71" s="67"/>
-      <c r="T71" s="67"/>
-      <c r="U71" s="67"/>
-      <c r="V71" s="67"/>
-      <c r="W71" s="67"/>
-      <c r="X71" s="68"/>
-    </row>
-    <row r="72" spans="2:36" s="60" customFormat="1" ht="18.75" customHeight="1">
+    <row r="71" spans="2:24" s="60" customFormat="1" ht="18.75" customHeight="1">
+      <c r="B71" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="C71" s="62" t="s">
+        <v>0</v>
+      </c>
+      <c r="D71" s="63">
+        <f>D48</f>
+        <v>0</v>
+      </c>
+      <c r="E71" s="63">
+        <f>E48</f>
+        <v>0</v>
+      </c>
+      <c r="F71" s="63">
+        <f>F48</f>
+        <v>0</v>
+      </c>
+      <c r="G71" s="63">
+        <f>G48</f>
+        <v>0</v>
+      </c>
+      <c r="H71" s="63">
+        <f>H48</f>
+        <v>0</v>
+      </c>
+      <c r="I71" s="63">
+        <f>I48</f>
+        <v>0</v>
+      </c>
+      <c r="J71" s="63">
+        <f>J48</f>
+        <v>0</v>
+      </c>
+      <c r="K71" s="63">
+        <f>K48</f>
+        <v>0</v>
+      </c>
+      <c r="L71" s="63">
+        <f>L48</f>
+        <v>0</v>
+      </c>
+      <c r="M71" s="63">
+        <f>M48</f>
+        <v>0</v>
+      </c>
+      <c r="N71" s="63">
+        <f>N48</f>
+        <v>0</v>
+      </c>
+      <c r="O71" s="63">
+        <f>O48</f>
+        <v>0</v>
+      </c>
+      <c r="P71" s="63">
+        <f>P48</f>
+        <v>0</v>
+      </c>
+      <c r="Q71" s="63">
+        <f>Q48</f>
+        <v>0</v>
+      </c>
+      <c r="R71" s="63">
+        <f>R48</f>
+        <v>0</v>
+      </c>
+      <c r="S71" s="63">
+        <f>S48</f>
+        <v>0</v>
+      </c>
+      <c r="T71" s="63">
+        <f>T48</f>
+        <v>0</v>
+      </c>
+      <c r="U71" s="63">
+        <f>U48</f>
+        <v>0</v>
+      </c>
+      <c r="V71" s="63">
+        <f>V48</f>
+        <v>0</v>
+      </c>
+      <c r="W71" s="63">
+        <f>W48</f>
+        <v>0</v>
+      </c>
+      <c r="X71" s="64"/>
+    </row>
+    <row r="72" spans="2:24" s="60" customFormat="1" ht="18.75" customHeight="1">
       <c r="B72" s="69" t="s">
-        <v>101</v>
-      </c>
-      <c r="C72" s="62"/>
-      <c r="D72" s="70" t="e">
-        <f>$C$44/$E$16</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E72" s="70" t="e">
-        <f t="shared" ref="E72:W72" si="8">$C$44/$E$16</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F72" s="70" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G72" s="70" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H72" s="70" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I72" s="70" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J72" s="70" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K72" s="70" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L72" s="70" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M72" s="70" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N72" s="70" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O72" s="70" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P72" s="70" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q72" s="70" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R72" s="70" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S72" s="70" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T72" s="70" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U72" s="70" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V72" s="70" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W72" s="70" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>13</v>
+      </c>
+      <c r="C72" s="62" t="s">
+        <v>0</v>
+      </c>
+      <c r="D72" s="63">
+        <f>D49</f>
+        <v>0</v>
+      </c>
+      <c r="E72" s="63">
+        <f>E49</f>
+        <v>0</v>
+      </c>
+      <c r="F72" s="63">
+        <f>F49</f>
+        <v>0</v>
+      </c>
+      <c r="G72" s="63">
+        <f>G49</f>
+        <v>0</v>
+      </c>
+      <c r="H72" s="63">
+        <f>H49</f>
+        <v>0</v>
+      </c>
+      <c r="I72" s="63">
+        <f>I49</f>
+        <v>0</v>
+      </c>
+      <c r="J72" s="63">
+        <f>J49</f>
+        <v>0</v>
+      </c>
+      <c r="K72" s="63">
+        <f>K49</f>
+        <v>0</v>
+      </c>
+      <c r="L72" s="63">
+        <f>L49</f>
+        <v>0</v>
+      </c>
+      <c r="M72" s="63">
+        <f>M49</f>
+        <v>0</v>
+      </c>
+      <c r="N72" s="63">
+        <f>N49</f>
+        <v>0</v>
+      </c>
+      <c r="O72" s="63">
+        <f>O49</f>
+        <v>0</v>
+      </c>
+      <c r="P72" s="63">
+        <f>P49</f>
+        <v>0</v>
+      </c>
+      <c r="Q72" s="63">
+        <f>Q49</f>
+        <v>0</v>
+      </c>
+      <c r="R72" s="63">
+        <f>R49</f>
+        <v>0</v>
+      </c>
+      <c r="S72" s="63">
+        <f>S49</f>
+        <v>0</v>
+      </c>
+      <c r="T72" s="63">
+        <f>T49</f>
+        <v>0</v>
+      </c>
+      <c r="U72" s="63">
+        <f>U49</f>
+        <v>0</v>
+      </c>
+      <c r="V72" s="63">
+        <f>V49</f>
+        <v>0</v>
+      </c>
+      <c r="W72" s="63">
+        <f>W49</f>
+        <v>0</v>
       </c>
       <c r="X72" s="64"/>
     </row>
-    <row r="73" spans="2:36" s="60" customFormat="1" ht="18.75" customHeight="1">
+    <row r="73" spans="2:24" s="60" customFormat="1" ht="18.75" customHeight="1">
       <c r="B73" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="C73" s="62" t="s">
-        <v>0</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="C73" s="62"/>
       <c r="D73" s="63">
-        <f>D45</f>
+        <f>D50</f>
         <v>0</v>
       </c>
       <c r="E73" s="63">
-        <f t="shared" ref="E73:W73" si="9">E45</f>
+        <f>E50</f>
         <v>0</v>
       </c>
       <c r="F73" s="63">
-        <f t="shared" si="9"/>
+        <f>F50</f>
         <v>0</v>
       </c>
       <c r="G73" s="63">
-        <f t="shared" si="9"/>
+        <f>G50</f>
         <v>0</v>
       </c>
       <c r="H73" s="63">
-        <f t="shared" si="9"/>
+        <f>H50</f>
         <v>0</v>
       </c>
       <c r="I73" s="63">
-        <f t="shared" si="9"/>
+        <f>I50</f>
         <v>0</v>
       </c>
       <c r="J73" s="63">
-        <f t="shared" si="9"/>
+        <f>J50</f>
         <v>0</v>
       </c>
       <c r="K73" s="63">
-        <f t="shared" si="9"/>
+        <f>K50</f>
         <v>0</v>
       </c>
       <c r="L73" s="63">
-        <f t="shared" si="9"/>
+        <f>L50</f>
         <v>0</v>
       </c>
       <c r="M73" s="63">
-        <f t="shared" si="9"/>
+        <f>M50</f>
         <v>0</v>
       </c>
       <c r="N73" s="63">
-        <f t="shared" si="9"/>
+        <f>N50</f>
         <v>0</v>
       </c>
       <c r="O73" s="63">
-        <f t="shared" si="9"/>
+        <f>O50</f>
         <v>0</v>
       </c>
       <c r="P73" s="63">
-        <f t="shared" si="9"/>
+        <f>P50</f>
         <v>0</v>
       </c>
       <c r="Q73" s="63">
-        <f t="shared" si="9"/>
+        <f>Q50</f>
         <v>0</v>
       </c>
       <c r="R73" s="63">
-        <f t="shared" si="9"/>
+        <f>R50</f>
         <v>0</v>
       </c>
       <c r="S73" s="63">
-        <f t="shared" si="9"/>
+        <f>S50</f>
         <v>0</v>
       </c>
       <c r="T73" s="63">
-        <f t="shared" si="9"/>
+        <f>T50</f>
         <v>0</v>
       </c>
       <c r="U73" s="63">
-        <f t="shared" si="9"/>
+        <f>U50</f>
         <v>0</v>
       </c>
       <c r="V73" s="63">
-        <f t="shared" si="9"/>
+        <f>V50</f>
         <v>0</v>
       </c>
       <c r="W73" s="63">
-        <f t="shared" si="9"/>
+        <f>W50</f>
         <v>0</v>
       </c>
       <c r="X73" s="64"/>
     </row>
-    <row r="74" spans="2:36" s="60" customFormat="1" ht="18.75" customHeight="1">
+    <row r="74" spans="2:24" s="60" customFormat="1" ht="18.75" customHeight="1">
       <c r="B74" s="69" t="s">
-        <v>10</v>
-      </c>
-      <c r="C74" s="62"/>
-      <c r="D74" s="63"/>
-      <c r="E74" s="63"/>
+        <v>15</v>
+      </c>
+      <c r="C74" s="71"/>
+      <c r="D74" s="72"/>
+      <c r="E74" s="73"/>
       <c r="F74" s="63"/>
       <c r="G74" s="63"/>
       <c r="H74" s="63"/>
@@ -5737,13 +5759,11 @@
       <c r="W74" s="63"/>
       <c r="X74" s="64"/>
     </row>
-    <row r="75" spans="2:36" s="60" customFormat="1" ht="18.75" customHeight="1">
+    <row r="75" spans="2:24" s="60" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
       <c r="B75" s="69" t="s">
-        <v>11</v>
-      </c>
-      <c r="C75" s="62" t="s">
-        <v>0</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="C75" s="71"/>
       <c r="D75" s="63"/>
       <c r="E75" s="63"/>
       <c r="F75" s="63"/>
@@ -5766,2140 +5786,1821 @@
       <c r="W75" s="63"/>
       <c r="X75" s="64"/>
     </row>
-    <row r="76" spans="2:36" s="60" customFormat="1" ht="18.75" customHeight="1">
-      <c r="B76" s="69" t="s">
-        <v>12</v>
-      </c>
-      <c r="C76" s="62" t="s">
-        <v>0</v>
-      </c>
-      <c r="D76" s="63">
-        <f>D48</f>
-        <v>0</v>
-      </c>
-      <c r="E76" s="63">
-        <f t="shared" ref="E76:W76" si="10">E48</f>
-        <v>0</v>
-      </c>
-      <c r="F76" s="63">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="G76" s="63">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="H76" s="63">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="I76" s="63">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="J76" s="63">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="K76" s="63">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="L76" s="63">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="M76" s="63">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="N76" s="63">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="O76" s="63">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="P76" s="63">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="Q76" s="63">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="R76" s="63">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="S76" s="63">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="T76" s="63">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="U76" s="63">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="V76" s="63">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="W76" s="63">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="X76" s="64"/>
-    </row>
-    <row r="77" spans="2:36" s="60" customFormat="1" ht="18.75" customHeight="1">
-      <c r="B77" s="69" t="s">
-        <v>13</v>
-      </c>
-      <c r="C77" s="62" t="s">
-        <v>0</v>
-      </c>
-      <c r="D77" s="63">
-        <f>D49</f>
-        <v>0</v>
-      </c>
-      <c r="E77" s="63">
-        <f t="shared" ref="E77:W77" si="11">E49</f>
-        <v>0</v>
-      </c>
-      <c r="F77" s="63">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="G77" s="63">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="H77" s="63">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="I77" s="63">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="J77" s="63">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="K77" s="63">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="L77" s="63">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="M77" s="63">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="N77" s="63">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="O77" s="63">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="P77" s="63">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="Q77" s="63">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="R77" s="63">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="S77" s="63">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="T77" s="63">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="U77" s="63">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="V77" s="63">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="W77" s="63">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="X77" s="64"/>
-    </row>
-    <row r="78" spans="2:36" s="60" customFormat="1" ht="18.75" customHeight="1">
-      <c r="B78" s="69" t="s">
-        <v>14</v>
-      </c>
-      <c r="C78" s="62"/>
-      <c r="D78" s="63">
-        <f>D50</f>
-        <v>0</v>
-      </c>
-      <c r="E78" s="63">
-        <f t="shared" ref="E78:W78" si="12">E50</f>
-        <v>0</v>
-      </c>
-      <c r="F78" s="63">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="G78" s="63">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="H78" s="63">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="I78" s="63">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="J78" s="63">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="K78" s="63">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="L78" s="63">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="M78" s="63">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="N78" s="63">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="O78" s="63">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="P78" s="63">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="Q78" s="63">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="R78" s="63">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="S78" s="63">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="T78" s="63">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="U78" s="63">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="V78" s="63">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="W78" s="63">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="X78" s="64"/>
-    </row>
-    <row r="79" spans="2:36" s="60" customFormat="1" ht="18.75" customHeight="1">
-      <c r="B79" s="69" t="s">
-        <v>15</v>
-      </c>
-      <c r="C79" s="71"/>
-      <c r="D79" s="72"/>
-      <c r="E79" s="73"/>
-      <c r="F79" s="63"/>
-      <c r="G79" s="63"/>
-      <c r="H79" s="63"/>
-      <c r="I79" s="63"/>
-      <c r="J79" s="63"/>
-      <c r="K79" s="63"/>
-      <c r="L79" s="63"/>
-      <c r="M79" s="63"/>
-      <c r="N79" s="63"/>
-      <c r="O79" s="63"/>
-      <c r="P79" s="63"/>
-      <c r="Q79" s="63"/>
-      <c r="R79" s="63"/>
-      <c r="S79" s="63"/>
-      <c r="T79" s="63"/>
-      <c r="U79" s="63"/>
-      <c r="V79" s="63"/>
-      <c r="W79" s="63"/>
-      <c r="X79" s="64"/>
-    </row>
-    <row r="80" spans="2:36" s="60" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B80" s="69" t="s">
-        <v>16</v>
-      </c>
-      <c r="C80" s="71"/>
-      <c r="D80" s="63"/>
-      <c r="E80" s="63"/>
-      <c r="F80" s="63"/>
-      <c r="G80" s="63"/>
-      <c r="H80" s="63"/>
-      <c r="I80" s="63"/>
-      <c r="J80" s="63"/>
-      <c r="K80" s="63"/>
-      <c r="L80" s="63"/>
-      <c r="M80" s="63"/>
-      <c r="N80" s="63"/>
-      <c r="O80" s="63"/>
-      <c r="P80" s="63"/>
-      <c r="Q80" s="63"/>
-      <c r="R80" s="63"/>
-      <c r="S80" s="63"/>
-      <c r="T80" s="63"/>
-      <c r="U80" s="63"/>
-      <c r="V80" s="63"/>
-      <c r="W80" s="63"/>
-      <c r="X80" s="64"/>
-    </row>
-    <row r="81" spans="2:25" s="60" customFormat="1" ht="18.75" customHeight="1">
-      <c r="B81" s="76" t="s">
-        <v>99</v>
-      </c>
-      <c r="C81" s="102"/>
-      <c r="D81" s="78" t="e">
-        <f>SUM(D69:D80)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E81" s="78" t="e">
-        <f t="shared" ref="E81:X81" si="13">SUM(E69:E80)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F81" s="78" t="e">
-        <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G81" s="78" t="e">
-        <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H81" s="78" t="e">
-        <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I81" s="78" t="e">
-        <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J81" s="78" t="e">
-        <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K81" s="78" t="e">
-        <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L81" s="78" t="e">
-        <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M81" s="78" t="e">
-        <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N81" s="78" t="e">
-        <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O81" s="78" t="e">
-        <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P81" s="78" t="e">
-        <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q81" s="78" t="e">
-        <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R81" s="78" t="e">
-        <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S81" s="78" t="e">
-        <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T81" s="78" t="e">
-        <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U81" s="78" t="e">
-        <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V81" s="78" t="e">
-        <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W81" s="78" t="e">
-        <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X81" s="78">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="2:25" s="60" customFormat="1" ht="18.75" customHeight="1">
-      <c r="B82" s="74" t="s">
+    <row r="76" spans="2:24" s="60" customFormat="1" ht="18.75" customHeight="1">
+      <c r="B76" s="76" t="s">
+        <v>94</v>
+      </c>
+      <c r="C76" s="87"/>
+      <c r="D76" s="78" t="e">
+        <f>SUM(D64:D75)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E76" s="78" t="e">
+        <f t="shared" ref="E76:X76" si="5">SUM(E64:E75)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F76" s="78" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G76" s="78" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H76" s="78" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I76" s="78" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J76" s="78" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K76" s="78" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L76" s="78" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M76" s="78" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N76" s="78" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O76" s="78" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="P76" s="78" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Q76" s="78" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R76" s="78" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S76" s="78" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T76" s="78" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U76" s="78" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V76" s="78" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W76" s="78" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X76" s="78">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="2:24" s="60" customFormat="1" ht="18.75" customHeight="1">
+      <c r="B77" s="74" t="s">
         <v>18</v>
       </c>
-      <c r="C82" s="71"/>
-      <c r="D82" s="63" t="e">
-        <f>-D81*0.2</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E82" s="63" t="e">
-        <f t="shared" ref="E82:X82" si="14">-E81*0.2</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F82" s="63" t="e">
-        <f t="shared" si="14"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G82" s="63" t="e">
-        <f t="shared" si="14"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H82" s="63" t="e">
-        <f t="shared" si="14"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I82" s="63" t="e">
-        <f t="shared" si="14"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J82" s="63" t="e">
-        <f t="shared" si="14"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K82" s="63" t="e">
-        <f t="shared" si="14"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L82" s="63" t="e">
-        <f t="shared" si="14"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M82" s="63" t="e">
-        <f t="shared" si="14"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N82" s="63" t="e">
-        <f t="shared" si="14"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O82" s="63" t="e">
-        <f t="shared" si="14"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P82" s="63" t="e">
-        <f t="shared" si="14"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q82" s="63" t="e">
-        <f t="shared" si="14"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R82" s="63" t="e">
-        <f t="shared" si="14"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S82" s="63" t="e">
-        <f t="shared" si="14"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T82" s="63" t="e">
-        <f t="shared" si="14"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U82" s="63" t="e">
-        <f t="shared" si="14"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V82" s="63" t="e">
-        <f t="shared" si="14"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W82" s="63" t="e">
-        <f t="shared" si="14"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X82" s="63">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="2:25" s="60" customFormat="1">
-      <c r="B83" s="103" t="s">
-        <v>100</v>
-      </c>
-      <c r="D83" s="104" t="e">
-        <f>SUM(D81:D82)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E83" s="104" t="e">
-        <f t="shared" ref="E83:X83" si="15">SUM(E81:E82)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F83" s="104" t="e">
-        <f t="shared" si="15"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G83" s="104" t="e">
-        <f t="shared" si="15"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H83" s="104" t="e">
-        <f t="shared" si="15"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I83" s="104" t="e">
-        <f t="shared" si="15"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J83" s="104" t="e">
-        <f t="shared" si="15"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K83" s="104" t="e">
-        <f t="shared" si="15"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L83" s="104" t="e">
-        <f t="shared" si="15"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M83" s="104" t="e">
-        <f t="shared" si="15"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N83" s="104" t="e">
-        <f t="shared" si="15"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O83" s="104" t="e">
-        <f t="shared" si="15"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P83" s="104" t="e">
-        <f t="shared" si="15"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q83" s="104" t="e">
-        <f t="shared" si="15"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R83" s="104" t="e">
-        <f t="shared" si="15"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S83" s="104" t="e">
-        <f t="shared" si="15"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T83" s="104" t="e">
-        <f t="shared" si="15"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U83" s="104" t="e">
-        <f t="shared" si="15"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V83" s="104" t="e">
-        <f t="shared" si="15"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W83" s="104" t="e">
-        <f t="shared" si="15"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X83" s="104">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="2:25" s="60" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B84" s="81" t="s">
+      <c r="C77" s="71"/>
+      <c r="D77" s="63" t="e">
+        <f>-D76*0.2</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E77" s="63" t="e">
+        <f t="shared" ref="E77:X77" si="6">-E76*0.2</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F77" s="63" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G77" s="63" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H77" s="63" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I77" s="63" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J77" s="63" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K77" s="63" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L77" s="63" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M77" s="63" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N77" s="63" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O77" s="63" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="P77" s="63" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Q77" s="63" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R77" s="63" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S77" s="63" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T77" s="63" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U77" s="63" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V77" s="63" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W77" s="63" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X77" s="63">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="2:24" s="60" customFormat="1" ht="15.4">
+      <c r="B78" s="88" t="s">
+        <v>95</v>
+      </c>
+      <c r="D78" s="89" t="e">
+        <f>SUM(D76:D77)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E78" s="89" t="e">
+        <f t="shared" ref="E78:X78" si="7">SUM(E76:E77)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F78" s="89" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G78" s="89" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H78" s="89" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I78" s="89" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J78" s="89" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K78" s="89" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L78" s="89" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M78" s="89" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N78" s="89" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O78" s="89" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="P78" s="89" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Q78" s="89" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R78" s="89" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S78" s="89" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T78" s="89" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U78" s="89" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V78" s="89" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W78" s="89" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X78" s="89">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" s="60" customFormat="1" ht="18.75" customHeight="1" thickBot="1">
+      <c r="B79" s="81" t="s">
         <v>20</v>
       </c>
-      <c r="C84" s="77"/>
-      <c r="D84" s="82"/>
-      <c r="E84" s="82"/>
-      <c r="F84" s="82"/>
-      <c r="G84" s="82"/>
-      <c r="H84" s="82"/>
-      <c r="I84" s="82"/>
-      <c r="J84" s="82"/>
-      <c r="K84" s="82"/>
-      <c r="L84" s="82"/>
-      <c r="M84" s="82"/>
-      <c r="N84" s="82"/>
-      <c r="O84" s="82"/>
-      <c r="P84" s="82"/>
-      <c r="Q84" s="82"/>
-      <c r="R84" s="82"/>
-      <c r="S84" s="82"/>
-      <c r="T84" s="82"/>
-      <c r="U84" s="82"/>
-      <c r="V84" s="82"/>
-      <c r="W84" s="82"/>
-      <c r="X84" s="105"/>
-    </row>
-    <row r="85" spans="2:25" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B85" s="34" t="s">
-        <v>26</v>
-      </c>
-      <c r="C85" s="35"/>
-      <c r="D85" s="36"/>
-      <c r="E85" s="36"/>
-      <c r="F85" s="36"/>
-      <c r="G85" s="36"/>
-      <c r="H85" s="36"/>
-      <c r="I85" s="36"/>
-      <c r="J85" s="36"/>
-      <c r="K85" s="36"/>
-      <c r="L85" s="36"/>
-      <c r="M85" s="36"/>
-      <c r="N85" s="36"/>
-      <c r="O85" s="36"/>
-      <c r="P85" s="36"/>
-      <c r="Q85" s="36"/>
-      <c r="R85" s="36"/>
-      <c r="S85" s="36"/>
-      <c r="T85" s="36"/>
-      <c r="U85" s="36"/>
-      <c r="V85" s="36"/>
-      <c r="W85" s="36"/>
-      <c r="X85" s="39"/>
-    </row>
-    <row r="86" spans="2:25" ht="18.75" customHeight="1">
-      <c r="B86" s="22"/>
-      <c r="C86" s="9"/>
-      <c r="D86" s="9"/>
-      <c r="E86" s="9"/>
-      <c r="F86" s="22"/>
-      <c r="G86" s="22"/>
-      <c r="H86" s="22"/>
-      <c r="I86" s="22"/>
-      <c r="J86" s="22"/>
-      <c r="K86" s="22"/>
-      <c r="L86" s="22"/>
-      <c r="M86" s="9"/>
-      <c r="N86" s="22"/>
-      <c r="O86" s="22"/>
-      <c r="P86" s="22"/>
-      <c r="Q86" s="22"/>
-      <c r="R86" s="22"/>
-      <c r="S86" s="22"/>
-      <c r="T86" s="22"/>
-      <c r="U86" s="22"/>
-      <c r="V86" s="22"/>
-      <c r="W86" s="22"/>
-      <c r="X86" s="22"/>
-    </row>
-    <row r="87" spans="2:25" customFormat="1" ht="18.75" customHeight="1">
-      <c r="C87" s="50" t="s">
+      <c r="C79" s="77"/>
+      <c r="D79" s="82"/>
+      <c r="E79" s="82"/>
+      <c r="F79" s="82"/>
+      <c r="G79" s="82"/>
+      <c r="H79" s="82"/>
+      <c r="I79" s="82"/>
+      <c r="J79" s="82"/>
+      <c r="K79" s="82"/>
+      <c r="L79" s="82"/>
+      <c r="M79" s="82"/>
+      <c r="N79" s="82"/>
+      <c r="O79" s="82"/>
+      <c r="P79" s="82"/>
+      <c r="Q79" s="82"/>
+      <c r="R79" s="82"/>
+      <c r="S79" s="82"/>
+      <c r="T79" s="82"/>
+      <c r="U79" s="82"/>
+      <c r="V79" s="82"/>
+      <c r="W79" s="82"/>
+      <c r="X79" s="90"/>
+    </row>
+    <row r="80" spans="2:24" ht="18.75" customHeight="1" thickBot="1">
+      <c r="B80" s="34" t="s">
+        <v>21</v>
+      </c>
+      <c r="C80" s="35"/>
+      <c r="D80" s="36"/>
+      <c r="E80" s="36"/>
+      <c r="F80" s="36"/>
+      <c r="G80" s="36"/>
+      <c r="H80" s="36"/>
+      <c r="I80" s="36"/>
+      <c r="J80" s="36"/>
+      <c r="K80" s="36"/>
+      <c r="L80" s="36"/>
+      <c r="M80" s="36"/>
+      <c r="N80" s="36"/>
+      <c r="O80" s="36"/>
+      <c r="P80" s="36"/>
+      <c r="Q80" s="36"/>
+      <c r="R80" s="36"/>
+      <c r="S80" s="36"/>
+      <c r="T80" s="36"/>
+      <c r="U80" s="36"/>
+      <c r="V80" s="36"/>
+      <c r="W80" s="36"/>
+      <c r="X80" s="39"/>
+    </row>
+    <row r="81" spans="2:25" ht="18.75" customHeight="1">
+      <c r="B81" s="22"/>
+      <c r="C81" s="9"/>
+      <c r="D81" s="9"/>
+      <c r="E81" s="9"/>
+      <c r="F81" s="22"/>
+      <c r="G81" s="22"/>
+      <c r="H81" s="22"/>
+      <c r="I81" s="22"/>
+      <c r="J81" s="22"/>
+      <c r="K81" s="22"/>
+      <c r="L81" s="22"/>
+      <c r="M81" s="9"/>
+      <c r="N81" s="22"/>
+      <c r="O81" s="22"/>
+      <c r="P81" s="22"/>
+      <c r="Q81" s="22"/>
+      <c r="R81" s="22"/>
+      <c r="S81" s="22"/>
+      <c r="T81" s="22"/>
+      <c r="U81" s="22"/>
+      <c r="V81" s="22"/>
+      <c r="W81" s="22"/>
+      <c r="X81" s="22"/>
+    </row>
+    <row r="82" spans="2:25" customFormat="1" ht="18.75" customHeight="1">
+      <c r="C82" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="D87" s="51">
+      <c r="D82" s="51">
         <f>D37</f>
         <v>2020</v>
       </c>
-      <c r="E87" s="51">
-        <f t="shared" ref="E87:W87" si="16">E37</f>
+      <c r="E82" s="51">
+        <f>E37</f>
         <v>2021</v>
       </c>
-      <c r="F87" s="51">
+      <c r="F82" s="51">
+        <f>F37</f>
+        <v>2022</v>
+      </c>
+      <c r="G82" s="51">
+        <f>G37</f>
+        <v>2023</v>
+      </c>
+      <c r="H82" s="51">
+        <f>H37</f>
+        <v>2024</v>
+      </c>
+      <c r="I82" s="51">
+        <f>I37</f>
+        <v>2025</v>
+      </c>
+      <c r="J82" s="51">
+        <f>J37</f>
+        <v>2026</v>
+      </c>
+      <c r="K82" s="51">
+        <f>K37</f>
+        <v>2027</v>
+      </c>
+      <c r="L82" s="51">
+        <f>L37</f>
+        <v>2028</v>
+      </c>
+      <c r="M82" s="51">
+        <f>M37</f>
+        <v>2029</v>
+      </c>
+      <c r="N82" s="51">
+        <f>N37</f>
+        <v>2030</v>
+      </c>
+      <c r="O82" s="51">
+        <f>O37</f>
+        <v>2031</v>
+      </c>
+      <c r="P82" s="51">
+        <f>P37</f>
+        <v>2032</v>
+      </c>
+      <c r="Q82" s="51">
+        <f>Q37</f>
+        <v>2033</v>
+      </c>
+      <c r="R82" s="51">
+        <f>R37</f>
+        <v>2034</v>
+      </c>
+      <c r="S82" s="51">
+        <f>S37</f>
+        <v>2035</v>
+      </c>
+      <c r="T82" s="51">
+        <f>T37</f>
+        <v>2036</v>
+      </c>
+      <c r="U82" s="51">
+        <f>U37</f>
+        <v>2037</v>
+      </c>
+      <c r="V82" s="51">
+        <f>V37</f>
+        <v>2038</v>
+      </c>
+      <c r="W82" s="51">
+        <f>W37</f>
+        <v>2039</v>
+      </c>
+      <c r="X82" s="52"/>
+    </row>
+    <row r="83" spans="2:25" ht="18.75" customHeight="1">
+      <c r="X83" s="40"/>
+    </row>
+    <row r="84" spans="2:25" customFormat="1" ht="18.75" customHeight="1">
+      <c r="B84" s="48" t="s">
+        <v>3</v>
+      </c>
+      <c r="C84" s="48">
+        <v>0</v>
+      </c>
+      <c r="D84" s="48">
+        <v>1</v>
+      </c>
+      <c r="E84" s="48">
+        <v>2</v>
+      </c>
+      <c r="F84" s="48">
+        <v>3</v>
+      </c>
+      <c r="G84" s="48">
+        <v>4</v>
+      </c>
+      <c r="H84" s="48">
+        <v>5</v>
+      </c>
+      <c r="I84" s="48">
+        <v>6</v>
+      </c>
+      <c r="J84" s="48">
+        <v>7</v>
+      </c>
+      <c r="K84" s="48">
+        <v>8</v>
+      </c>
+      <c r="L84" s="48">
+        <v>9</v>
+      </c>
+      <c r="M84" s="48">
+        <v>10</v>
+      </c>
+      <c r="N84" s="48">
+        <v>11</v>
+      </c>
+      <c r="O84" s="48">
+        <v>12</v>
+      </c>
+      <c r="P84" s="48">
+        <v>13</v>
+      </c>
+      <c r="Q84" s="48">
+        <v>14</v>
+      </c>
+      <c r="R84" s="48">
+        <v>15</v>
+      </c>
+      <c r="S84" s="48">
+        <v>16</v>
+      </c>
+      <c r="T84" s="48">
+        <v>17</v>
+      </c>
+      <c r="U84" s="48">
+        <v>18</v>
+      </c>
+      <c r="V84" s="48">
+        <v>19</v>
+      </c>
+      <c r="W84" s="48">
+        <v>20</v>
+      </c>
+      <c r="X84" s="49"/>
+    </row>
+    <row r="85" spans="2:25" s="60" customFormat="1" ht="18.75" customHeight="1">
+      <c r="B85" s="91" t="s">
+        <v>23</v>
+      </c>
+      <c r="C85" s="91"/>
+      <c r="D85" s="92" t="e">
+        <f>D78</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E85" s="92" t="e">
+        <f t="shared" ref="E85:W85" si="8">E78</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F85" s="92" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G85" s="92" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H85" s="92" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I85" s="92" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J85" s="92" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K85" s="92" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L85" s="92" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M85" s="92" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N85" s="92" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O85" s="92" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="P85" s="92" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Q85" s="92" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R85" s="92" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S85" s="92" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T85" s="92" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U85" s="92" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V85" s="92" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W85" s="92" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X85" s="91"/>
+      <c r="Y85" s="91"/>
+    </row>
+    <row r="86" spans="2:25" s="60" customFormat="1" ht="15.4">
+      <c r="B86" s="91" t="s">
+        <v>24</v>
+      </c>
+      <c r="C86" s="91"/>
+      <c r="D86" s="106" t="e">
+        <f>-D67</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E86" s="106" t="e">
+        <f t="shared" ref="E86:W86" si="9">-E67</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F86" s="106" t="e">
+        <f t="shared" si="9"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G86" s="106" t="e">
+        <f t="shared" si="9"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H86" s="106" t="e">
+        <f t="shared" si="9"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I86" s="106" t="e">
+        <f t="shared" si="9"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J86" s="106" t="e">
+        <f t="shared" si="9"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K86" s="106" t="e">
+        <f t="shared" si="9"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L86" s="106" t="e">
+        <f t="shared" si="9"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M86" s="106" t="e">
+        <f t="shared" si="9"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N86" s="106" t="e">
+        <f t="shared" si="9"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O86" s="106" t="e">
+        <f t="shared" si="9"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="P86" s="106" t="e">
+        <f t="shared" si="9"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Q86" s="106" t="e">
+        <f t="shared" si="9"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R86" s="106" t="e">
+        <f t="shared" si="9"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S86" s="106" t="e">
+        <f t="shared" si="9"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T86" s="106" t="e">
+        <f t="shared" si="9"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U86" s="106" t="e">
+        <f t="shared" si="9"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V86" s="106" t="e">
+        <f t="shared" si="9"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W86" s="106" t="e">
+        <f t="shared" si="9"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X86" s="83"/>
+    </row>
+    <row r="87" spans="2:25" s="60" customFormat="1" ht="15.4">
+      <c r="B87" s="91" t="s">
+        <v>25</v>
+      </c>
+      <c r="C87" s="91"/>
+      <c r="D87" s="93" t="e">
+        <f>SUM(D85:D86)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E87" s="93" t="e">
+        <f t="shared" ref="E87:W87" si="10">SUM(E85:E86)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F87" s="93" t="e">
+        <f t="shared" si="10"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G87" s="93" t="e">
+        <f t="shared" si="10"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H87" s="93" t="e">
+        <f t="shared" si="10"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I87" s="93" t="e">
+        <f t="shared" si="10"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J87" s="93" t="e">
+        <f t="shared" si="10"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K87" s="93" t="e">
+        <f t="shared" si="10"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L87" s="93" t="e">
+        <f t="shared" si="10"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M87" s="93" t="e">
+        <f t="shared" si="10"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N87" s="93" t="e">
+        <f t="shared" si="10"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O87" s="93" t="e">
+        <f t="shared" si="10"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="P87" s="93" t="e">
+        <f t="shared" si="10"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Q87" s="93" t="e">
+        <f t="shared" si="10"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R87" s="93" t="e">
+        <f t="shared" si="10"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S87" s="93" t="e">
+        <f t="shared" si="10"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T87" s="93" t="e">
+        <f t="shared" si="10"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U87" s="93" t="e">
+        <f t="shared" si="10"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V87" s="93" t="e">
+        <f t="shared" si="10"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W87" s="93" t="e">
+        <f t="shared" si="10"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X87" s="94"/>
+    </row>
+    <row r="88" spans="2:25" s="60" customFormat="1" ht="15.4">
+      <c r="B88" s="91"/>
+      <c r="C88" s="91"/>
+      <c r="D88" s="91"/>
+      <c r="E88" s="91"/>
+      <c r="F88" s="95"/>
+      <c r="G88" s="95"/>
+      <c r="H88" s="95"/>
+      <c r="I88" s="95"/>
+      <c r="J88" s="95"/>
+      <c r="K88" s="95"/>
+      <c r="L88" s="95"/>
+      <c r="M88" s="95"/>
+      <c r="N88" s="95"/>
+      <c r="O88" s="95"/>
+      <c r="P88" s="95"/>
+      <c r="Q88" s="95"/>
+      <c r="R88" s="95"/>
+      <c r="S88" s="95"/>
+      <c r="T88" s="95"/>
+      <c r="U88" s="95"/>
+      <c r="V88" s="95"/>
+      <c r="W88" s="95"/>
+      <c r="X88" s="96"/>
+    </row>
+    <row r="89" spans="2:25" s="60" customFormat="1" ht="15.4">
+      <c r="B89" s="97" t="s">
+        <v>26</v>
+      </c>
+      <c r="C89" s="98"/>
+      <c r="D89" s="99">
+        <f>C44</f>
+        <v>0</v>
+      </c>
+      <c r="E89" s="98"/>
+      <c r="F89" s="98"/>
+      <c r="G89" s="98"/>
+      <c r="H89" s="98"/>
+      <c r="I89" s="98"/>
+      <c r="J89" s="98"/>
+      <c r="K89" s="98"/>
+      <c r="L89" s="98"/>
+      <c r="M89" s="98"/>
+      <c r="N89" s="98"/>
+      <c r="O89" s="98"/>
+      <c r="P89" s="98"/>
+      <c r="Q89" s="98"/>
+      <c r="R89" s="98"/>
+      <c r="S89" s="98"/>
+      <c r="T89" s="98"/>
+      <c r="U89" s="98"/>
+      <c r="V89" s="98"/>
+      <c r="W89" s="98"/>
+      <c r="X89" s="83"/>
+    </row>
+    <row r="90" spans="2:25" s="60" customFormat="1" ht="15.4">
+      <c r="B90" s="91"/>
+      <c r="C90" s="91"/>
+      <c r="D90" s="91"/>
+      <c r="E90" s="91"/>
+      <c r="F90" s="95"/>
+      <c r="G90" s="95"/>
+      <c r="H90" s="95"/>
+      <c r="I90" s="95"/>
+      <c r="J90" s="95"/>
+      <c r="K90" s="95"/>
+      <c r="L90" s="95"/>
+      <c r="M90" s="95"/>
+      <c r="N90" s="95"/>
+      <c r="O90" s="95"/>
+      <c r="P90" s="95"/>
+      <c r="Q90" s="95"/>
+      <c r="R90" s="95"/>
+      <c r="S90" s="95"/>
+      <c r="T90" s="95"/>
+      <c r="U90" s="95"/>
+      <c r="V90" s="95"/>
+      <c r="W90" s="95"/>
+      <c r="X90" s="96"/>
+    </row>
+    <row r="91" spans="2:25" s="60" customFormat="1" ht="15.4">
+      <c r="B91" s="91"/>
+      <c r="C91" s="91"/>
+      <c r="D91" s="91"/>
+      <c r="E91" s="91"/>
+      <c r="F91" s="95"/>
+      <c r="G91" s="95"/>
+      <c r="H91" s="95"/>
+      <c r="I91" s="95"/>
+      <c r="J91" s="95"/>
+      <c r="K91" s="95"/>
+      <c r="L91" s="95"/>
+      <c r="M91" s="95"/>
+      <c r="N91" s="95"/>
+      <c r="O91" s="95"/>
+      <c r="P91" s="95"/>
+      <c r="Q91" s="95"/>
+      <c r="R91" s="95"/>
+      <c r="S91" s="95"/>
+      <c r="T91" s="95"/>
+      <c r="U91" s="95"/>
+      <c r="V91" s="95"/>
+      <c r="W91" s="95"/>
+      <c r="X91" s="96"/>
+    </row>
+    <row r="92" spans="2:25" s="60" customFormat="1" ht="15.4">
+      <c r="B92" s="97" t="s">
+        <v>27</v>
+      </c>
+      <c r="C92" s="98"/>
+      <c r="D92" s="99">
+        <f>-D89*D31</f>
+        <v>0</v>
+      </c>
+      <c r="E92" s="98"/>
+      <c r="F92" s="98"/>
+      <c r="G92" s="98"/>
+      <c r="H92" s="98"/>
+      <c r="I92" s="98"/>
+      <c r="J92" s="98"/>
+      <c r="K92" s="98"/>
+      <c r="L92" s="98"/>
+      <c r="M92" s="98"/>
+      <c r="N92" s="98"/>
+      <c r="O92" s="98"/>
+      <c r="P92" s="98"/>
+      <c r="Q92" s="98"/>
+      <c r="R92" s="98"/>
+      <c r="S92" s="98"/>
+      <c r="T92" s="98"/>
+      <c r="U92" s="98"/>
+      <c r="V92" s="98"/>
+      <c r="W92" s="98"/>
+      <c r="X92" s="96"/>
+    </row>
+    <row r="93" spans="2:25" s="60" customFormat="1" ht="15.4">
+      <c r="B93" s="91" t="s">
+        <v>28</v>
+      </c>
+      <c r="C93" s="91"/>
+      <c r="D93" s="91"/>
+      <c r="E93" s="91"/>
+      <c r="F93" s="91"/>
+      <c r="G93" s="91"/>
+      <c r="H93" s="91"/>
+      <c r="I93" s="91"/>
+      <c r="J93" s="91"/>
+      <c r="K93" s="91"/>
+      <c r="L93" s="91"/>
+      <c r="M93" s="91"/>
+      <c r="N93" s="91"/>
+      <c r="O93" s="91"/>
+      <c r="P93" s="91"/>
+      <c r="Q93" s="91"/>
+      <c r="R93" s="91"/>
+      <c r="S93" s="91"/>
+      <c r="T93" s="95"/>
+      <c r="U93" s="95"/>
+      <c r="V93" s="95"/>
+      <c r="W93" s="95"/>
+      <c r="X93" s="83"/>
+    </row>
+    <row r="94" spans="2:25" s="60" customFormat="1" ht="15.4">
+      <c r="B94" s="91" t="s">
+        <v>29</v>
+      </c>
+      <c r="C94" s="95"/>
+      <c r="D94" s="92">
+        <f>-D89*(1-D31)</f>
+        <v>0</v>
+      </c>
+      <c r="E94" s="95"/>
+      <c r="F94" s="95"/>
+      <c r="G94" s="95"/>
+      <c r="H94" s="95"/>
+      <c r="I94" s="95"/>
+      <c r="J94" s="95"/>
+      <c r="K94" s="95"/>
+      <c r="L94" s="95"/>
+      <c r="M94" s="95"/>
+      <c r="N94" s="95"/>
+      <c r="O94" s="95"/>
+      <c r="P94" s="95"/>
+      <c r="Q94" s="95"/>
+      <c r="R94" s="95"/>
+      <c r="S94" s="95"/>
+      <c r="T94" s="95"/>
+      <c r="U94" s="95"/>
+      <c r="V94" s="95"/>
+      <c r="W94" s="95"/>
+      <c r="X94" s="94"/>
+    </row>
+    <row r="95" spans="2:25" s="60" customFormat="1" ht="15.4">
+      <c r="B95" s="91" t="s">
+        <v>30</v>
+      </c>
+      <c r="C95" s="95"/>
+      <c r="D95" s="95"/>
+      <c r="E95" s="110" t="e">
+        <f>-D85*$D$33</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F95" s="110" t="e">
+        <f t="shared" ref="F95:W95" si="11">-E85*$D$33</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G95" s="110" t="e">
+        <f t="shared" si="11"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H95" s="110" t="e">
+        <f t="shared" si="11"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I95" s="110" t="e">
+        <f t="shared" si="11"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J95" s="110" t="e">
+        <f t="shared" si="11"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K95" s="110" t="e">
+        <f t="shared" si="11"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L95" s="110" t="e">
+        <f t="shared" si="11"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M95" s="110" t="e">
+        <f t="shared" si="11"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N95" s="110" t="e">
+        <f t="shared" si="11"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O95" s="110" t="e">
+        <f t="shared" si="11"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="P95" s="110" t="e">
+        <f t="shared" si="11"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Q95" s="110" t="e">
+        <f t="shared" si="11"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R95" s="110" t="e">
+        <f t="shared" si="11"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S95" s="110" t="e">
+        <f t="shared" si="11"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T95" s="110" t="e">
+        <f t="shared" si="11"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U95" s="110" t="e">
+        <f t="shared" si="11"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V95" s="110" t="e">
+        <f t="shared" si="11"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W95" s="110" t="e">
+        <f t="shared" si="11"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X95" s="111" t="e">
+        <f>-W85</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="96" spans="2:25" s="60" customFormat="1" ht="15.4">
+      <c r="B96" s="100" t="s">
+        <v>31</v>
+      </c>
+      <c r="C96" s="101"/>
+      <c r="D96" s="101"/>
+      <c r="E96" s="112"/>
+      <c r="F96" s="112"/>
+      <c r="G96" s="112"/>
+      <c r="H96" s="112"/>
+      <c r="I96" s="112"/>
+      <c r="J96" s="112"/>
+      <c r="K96" s="112"/>
+      <c r="L96" s="112"/>
+      <c r="M96" s="112"/>
+      <c r="N96" s="112"/>
+      <c r="O96" s="112"/>
+      <c r="P96" s="112"/>
+      <c r="Q96" s="112"/>
+      <c r="R96" s="113"/>
+      <c r="S96" s="113"/>
+      <c r="T96" s="113"/>
+      <c r="U96" s="113"/>
+      <c r="V96" s="112"/>
+      <c r="W96" s="112"/>
+      <c r="X96" s="111" t="e">
+        <f>-W101-X95</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="97" spans="2:24" s="60" customFormat="1" ht="15.4">
+      <c r="B97" s="95"/>
+      <c r="C97" s="95"/>
+      <c r="D97" s="95"/>
+      <c r="E97" s="95"/>
+      <c r="F97" s="95"/>
+      <c r="G97" s="95"/>
+      <c r="H97" s="95"/>
+      <c r="I97" s="95"/>
+      <c r="J97" s="95"/>
+      <c r="K97" s="95"/>
+      <c r="L97" s="95"/>
+      <c r="M97" s="95"/>
+      <c r="N97" s="95"/>
+      <c r="O97" s="95"/>
+      <c r="P97" s="95"/>
+      <c r="Q97" s="95"/>
+      <c r="R97" s="95"/>
+      <c r="S97" s="95"/>
+      <c r="T97" s="95"/>
+      <c r="U97" s="95"/>
+      <c r="V97" s="95"/>
+      <c r="W97" s="95"/>
+      <c r="X97" s="94"/>
+    </row>
+    <row r="98" spans="2:24" s="60" customFormat="1" ht="15.4">
+      <c r="B98" s="95"/>
+      <c r="C98" s="95"/>
+      <c r="D98" s="95"/>
+      <c r="E98" s="95"/>
+      <c r="F98" s="95"/>
+      <c r="G98" s="95"/>
+      <c r="H98" s="95"/>
+      <c r="I98" s="95"/>
+      <c r="J98" s="95"/>
+      <c r="K98" s="95"/>
+      <c r="L98" s="95"/>
+      <c r="M98" s="95"/>
+      <c r="N98" s="95"/>
+      <c r="O98" s="95"/>
+      <c r="P98" s="95"/>
+      <c r="Q98" s="95"/>
+      <c r="R98" s="95"/>
+      <c r="S98" s="95"/>
+      <c r="T98" s="95"/>
+      <c r="U98" s="95"/>
+      <c r="V98" s="95"/>
+      <c r="W98" s="95"/>
+      <c r="X98" s="94"/>
+    </row>
+    <row r="99" spans="2:24" s="60" customFormat="1" ht="16.149999999999999">
+      <c r="B99" s="91" t="s">
+        <v>32</v>
+      </c>
+      <c r="C99" s="102">
+        <v>0</v>
+      </c>
+      <c r="D99" s="92" t="e">
+        <f>SUM(D87:D96)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E99" s="92" t="e">
+        <f t="shared" ref="E99:W99" si="12">SUM(E87:E96)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F99" s="92" t="e">
+        <f t="shared" si="12"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G99" s="92" t="e">
+        <f t="shared" si="12"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H99" s="92" t="e">
+        <f t="shared" si="12"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I99" s="92" t="e">
+        <f t="shared" si="12"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J99" s="92" t="e">
+        <f t="shared" si="12"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K99" s="92" t="e">
+        <f t="shared" si="12"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L99" s="92" t="e">
+        <f t="shared" si="12"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M99" s="92" t="e">
+        <f t="shared" si="12"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N99" s="92" t="e">
+        <f t="shared" si="12"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O99" s="92" t="e">
+        <f t="shared" si="12"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="P99" s="92" t="e">
+        <f t="shared" si="12"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Q99" s="92" t="e">
+        <f t="shared" si="12"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R99" s="92" t="e">
+        <f t="shared" si="12"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S99" s="92" t="e">
+        <f t="shared" si="12"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T99" s="92" t="e">
+        <f t="shared" si="12"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U99" s="92" t="e">
+        <f t="shared" si="12"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V99" s="92" t="e">
+        <f t="shared" si="12"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W99" s="92" t="e">
+        <f t="shared" si="12"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X99" s="94"/>
+    </row>
+    <row r="100" spans="2:24" s="60" customFormat="1" ht="15.4">
+      <c r="B100" s="91" t="s">
+        <v>33</v>
+      </c>
+      <c r="C100" s="92">
+        <v>0</v>
+      </c>
+      <c r="D100" s="92">
+        <f>C101</f>
+        <v>0</v>
+      </c>
+      <c r="E100" s="92" t="e">
+        <f>D101</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F100" s="92" t="e">
+        <f>E101</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G100" s="92" t="e">
+        <f t="shared" ref="G100:W100" si="13">F101</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H100" s="92" t="e">
+        <f t="shared" si="13"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I100" s="92" t="e">
+        <f t="shared" si="13"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J100" s="92" t="e">
+        <f t="shared" si="13"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K100" s="92" t="e">
+        <f t="shared" si="13"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L100" s="92" t="e">
+        <f t="shared" si="13"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M100" s="92" t="e">
+        <f t="shared" si="13"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N100" s="92" t="e">
+        <f t="shared" si="13"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O100" s="92" t="e">
+        <f t="shared" si="13"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="P100" s="92" t="e">
+        <f t="shared" si="13"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Q100" s="92" t="e">
+        <f t="shared" si="13"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R100" s="92" t="e">
+        <f t="shared" si="13"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S100" s="92" t="e">
+        <f t="shared" si="13"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T100" s="92" t="e">
+        <f t="shared" si="13"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U100" s="92" t="e">
+        <f t="shared" si="13"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V100" s="92" t="e">
+        <f t="shared" si="13"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W100" s="92" t="e">
+        <f t="shared" si="13"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X100" s="96"/>
+    </row>
+    <row r="101" spans="2:24" s="60" customFormat="1" ht="15.4">
+      <c r="B101" s="91" t="s">
+        <v>34</v>
+      </c>
+      <c r="C101" s="92">
+        <v>0</v>
+      </c>
+      <c r="D101" s="92" t="e">
+        <f>D99+D100</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E101" s="92" t="e">
+        <f>E99+E100</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F101" s="92" t="e">
+        <f t="shared" ref="F101:W101" si="14">F99+F100</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G101" s="92" t="e">
+        <f t="shared" si="14"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H101" s="92" t="e">
+        <f t="shared" si="14"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I101" s="92" t="e">
+        <f t="shared" si="14"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J101" s="92" t="e">
+        <f t="shared" si="14"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K101" s="92" t="e">
+        <f t="shared" si="14"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L101" s="92" t="e">
+        <f t="shared" si="14"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M101" s="92" t="e">
+        <f t="shared" si="14"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N101" s="92" t="e">
+        <f t="shared" si="14"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O101" s="92" t="e">
+        <f t="shared" si="14"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="P101" s="92" t="e">
+        <f t="shared" si="14"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Q101" s="92" t="e">
+        <f t="shared" si="14"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R101" s="92" t="e">
+        <f t="shared" si="14"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S101" s="92" t="e">
+        <f t="shared" si="14"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T101" s="92" t="e">
+        <f t="shared" si="14"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U101" s="92" t="e">
+        <f t="shared" si="14"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V101" s="92" t="e">
+        <f t="shared" si="14"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W101" s="92" t="e">
+        <f t="shared" si="14"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X101" s="96"/>
+    </row>
+    <row r="102" spans="2:24" s="60" customFormat="1" ht="15.4">
+      <c r="B102" s="91"/>
+      <c r="C102" s="91"/>
+      <c r="D102" s="91"/>
+      <c r="E102" s="91"/>
+      <c r="F102" s="91"/>
+      <c r="G102" s="91"/>
+      <c r="H102" s="91"/>
+      <c r="I102" s="91"/>
+      <c r="J102" s="91"/>
+      <c r="K102" s="91"/>
+      <c r="L102" s="91"/>
+      <c r="M102" s="91"/>
+      <c r="N102" s="91"/>
+      <c r="O102" s="91"/>
+      <c r="P102" s="91"/>
+      <c r="Q102" s="91"/>
+      <c r="R102" s="91"/>
+      <c r="S102" s="91"/>
+      <c r="T102" s="91"/>
+      <c r="U102" s="91"/>
+      <c r="V102" s="91"/>
+      <c r="W102" s="91"/>
+      <c r="X102" s="91"/>
+    </row>
+    <row r="103" spans="2:24" s="60" customFormat="1" ht="15.4">
+      <c r="B103" s="91"/>
+      <c r="C103" s="91"/>
+      <c r="D103" s="91"/>
+      <c r="E103" s="91"/>
+      <c r="F103" s="95"/>
+      <c r="G103" s="91"/>
+      <c r="H103" s="91"/>
+      <c r="I103" s="91"/>
+      <c r="J103" s="91"/>
+      <c r="K103" s="91"/>
+      <c r="L103" s="91"/>
+      <c r="M103" s="91"/>
+      <c r="N103" s="91"/>
+      <c r="O103" s="91"/>
+      <c r="P103" s="91"/>
+      <c r="Q103" s="91"/>
+      <c r="R103" s="91"/>
+      <c r="S103" s="91"/>
+      <c r="T103" s="91"/>
+      <c r="U103" s="91"/>
+      <c r="V103" s="91"/>
+      <c r="W103" s="91"/>
+      <c r="X103" s="91"/>
+    </row>
+    <row r="104" spans="2:24" s="60" customFormat="1" ht="15.4">
+      <c r="B104" s="103" t="s">
+        <v>35</v>
+      </c>
+      <c r="C104" s="104"/>
+      <c r="D104" s="105">
+        <f>-D94</f>
+        <v>0</v>
+      </c>
+      <c r="E104" s="93" t="e">
+        <f>-E95-E96</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F104" s="93" t="e">
+        <f t="shared" ref="F104:X104" si="15">-F95-F96</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G104" s="93" t="e">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H104" s="93" t="e">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I104" s="93" t="e">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J104" s="93" t="e">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K104" s="93" t="e">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L104" s="93" t="e">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M104" s="93" t="e">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N104" s="93" t="e">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O104" s="93" t="e">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="P104" s="93" t="e">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Q104" s="93" t="e">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R104" s="93" t="e">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S104" s="93" t="e">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T104" s="93" t="e">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U104" s="93" t="e">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V104" s="93" t="e">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W104" s="93" t="e">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X104" s="93" t="e">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="105" spans="2:24" s="60" customFormat="1" ht="15.4">
+      <c r="B105" s="91" t="s">
+        <v>36</v>
+      </c>
+      <c r="C105" s="108" t="e">
+        <f>IRR(D104:X104)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D105" s="95"/>
+      <c r="E105" s="95"/>
+      <c r="F105" s="91"/>
+      <c r="G105" s="91"/>
+      <c r="H105" s="91"/>
+      <c r="I105" s="91"/>
+      <c r="J105" s="91"/>
+      <c r="K105" s="91"/>
+      <c r="L105" s="91"/>
+      <c r="M105" s="91"/>
+      <c r="N105" s="91"/>
+      <c r="O105" s="91"/>
+      <c r="P105" s="91"/>
+      <c r="Q105" s="91"/>
+      <c r="R105" s="91"/>
+      <c r="S105" s="91"/>
+      <c r="T105" s="91"/>
+      <c r="U105" s="91"/>
+      <c r="V105" s="91"/>
+      <c r="W105" s="91"/>
+      <c r="X105" s="91"/>
+    </row>
+    <row r="106" spans="2:24" s="60" customFormat="1" ht="15.4">
+      <c r="B106" s="103" t="s">
+        <v>37</v>
+      </c>
+      <c r="C106" s="104"/>
+      <c r="D106" s="105" t="e">
+        <f>D85-D94</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E106" s="93" t="e">
+        <f>E85</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F106" s="93" t="e">
+        <f>F85-F96</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G106" s="93" t="e">
+        <f t="shared" ref="G106:W106" si="16">G85-G96</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H106" s="93" t="e">
         <f t="shared" si="16"/>
-        <v>2022</v>
-      </c>
-      <c r="G87" s="51">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I106" s="93" t="e">
         <f t="shared" si="16"/>
-        <v>2023</v>
-      </c>
-      <c r="H87" s="51">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J106" s="93" t="e">
         <f t="shared" si="16"/>
-        <v>2024</v>
-      </c>
-      <c r="I87" s="51">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K106" s="93" t="e">
         <f t="shared" si="16"/>
-        <v>2025</v>
-      </c>
-      <c r="J87" s="51">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L106" s="93" t="e">
         <f t="shared" si="16"/>
-        <v>2026</v>
-      </c>
-      <c r="K87" s="51">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M106" s="93" t="e">
         <f t="shared" si="16"/>
-        <v>2027</v>
-      </c>
-      <c r="L87" s="51">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N106" s="93" t="e">
         <f t="shared" si="16"/>
-        <v>2028</v>
-      </c>
-      <c r="M87" s="51">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O106" s="93" t="e">
         <f t="shared" si="16"/>
-        <v>2029</v>
-      </c>
-      <c r="N87" s="51">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="P106" s="93" t="e">
         <f t="shared" si="16"/>
-        <v>2030</v>
-      </c>
-      <c r="O87" s="51">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Q106" s="93" t="e">
         <f t="shared" si="16"/>
-        <v>2031</v>
-      </c>
-      <c r="P87" s="51">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R106" s="93" t="e">
         <f t="shared" si="16"/>
-        <v>2032</v>
-      </c>
-      <c r="Q87" s="51">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S106" s="93" t="e">
         <f t="shared" si="16"/>
-        <v>2033</v>
-      </c>
-      <c r="R87" s="51">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T106" s="93" t="e">
         <f t="shared" si="16"/>
-        <v>2034</v>
-      </c>
-      <c r="S87" s="51">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U106" s="93" t="e">
         <f t="shared" si="16"/>
-        <v>2035</v>
-      </c>
-      <c r="T87" s="51">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V106" s="93" t="e">
         <f t="shared" si="16"/>
-        <v>2036</v>
-      </c>
-      <c r="U87" s="51">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W106" s="93" t="e">
         <f t="shared" si="16"/>
-        <v>2037</v>
-      </c>
-      <c r="V87" s="51">
-        <f t="shared" si="16"/>
-        <v>2038</v>
-      </c>
-      <c r="W87" s="51">
-        <f t="shared" si="16"/>
-        <v>2039</v>
-      </c>
-      <c r="X87" s="52"/>
-    </row>
-    <row r="88" spans="2:25" ht="18.75" customHeight="1">
-      <c r="X88" s="40"/>
-    </row>
-    <row r="89" spans="2:25" customFormat="1" ht="18.75" customHeight="1">
-      <c r="B89" s="48" t="s">
-        <v>3</v>
-      </c>
-      <c r="C89" s="48">
-        <v>0</v>
-      </c>
-      <c r="D89" s="48">
-        <v>1</v>
-      </c>
-      <c r="E89" s="48">
-        <v>2</v>
-      </c>
-      <c r="F89" s="48">
-        <v>3</v>
-      </c>
-      <c r="G89" s="48">
-        <v>4</v>
-      </c>
-      <c r="H89" s="48">
-        <v>5</v>
-      </c>
-      <c r="I89" s="48">
-        <v>6</v>
-      </c>
-      <c r="J89" s="48">
-        <v>7</v>
-      </c>
-      <c r="K89" s="48">
-        <v>8</v>
-      </c>
-      <c r="L89" s="48">
-        <v>9</v>
-      </c>
-      <c r="M89" s="48">
-        <v>10</v>
-      </c>
-      <c r="N89" s="48">
-        <v>11</v>
-      </c>
-      <c r="O89" s="48">
-        <v>12</v>
-      </c>
-      <c r="P89" s="48">
-        <v>13</v>
-      </c>
-      <c r="Q89" s="48">
-        <v>14</v>
-      </c>
-      <c r="R89" s="48">
-        <v>15</v>
-      </c>
-      <c r="S89" s="48">
-        <v>16</v>
-      </c>
-      <c r="T89" s="48">
-        <v>17</v>
-      </c>
-      <c r="U89" s="48">
-        <v>18</v>
-      </c>
-      <c r="V89" s="48">
-        <v>19</v>
-      </c>
-      <c r="W89" s="48">
-        <v>20</v>
-      </c>
-      <c r="X89" s="49"/>
-    </row>
-    <row r="90" spans="2:25" s="60" customFormat="1" ht="18.75" customHeight="1">
-      <c r="B90" s="106" t="s">
-        <v>28</v>
-      </c>
-      <c r="C90" s="106"/>
-      <c r="D90" s="107" t="e">
-        <f>D83</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E90" s="107" t="e">
-        <f t="shared" ref="E90:W90" si="17">E83</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F90" s="107" t="e">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X106" s="83"/>
+    </row>
+    <row r="107" spans="2:24" s="60" customFormat="1" ht="15.4">
+      <c r="B107" s="103" t="s">
+        <v>38</v>
+      </c>
+      <c r="C107" s="107" t="e">
+        <f>IRR(D106:W106)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D107" s="95"/>
+      <c r="E107" s="95"/>
+      <c r="F107" s="91"/>
+      <c r="G107" s="91"/>
+      <c r="H107" s="91"/>
+      <c r="I107" s="91"/>
+      <c r="J107" s="91"/>
+      <c r="K107" s="91"/>
+      <c r="L107" s="91"/>
+      <c r="M107" s="91"/>
+      <c r="N107" s="91"/>
+      <c r="O107" s="91"/>
+      <c r="P107" s="91"/>
+      <c r="Q107" s="91"/>
+      <c r="R107" s="91"/>
+      <c r="S107" s="91"/>
+      <c r="T107" s="91"/>
+      <c r="U107" s="91"/>
+      <c r="V107" s="91"/>
+      <c r="W107" s="91"/>
+      <c r="X107" s="91"/>
+    </row>
+    <row r="108" spans="2:24" s="60" customFormat="1" ht="15.4">
+      <c r="B108" s="91"/>
+      <c r="C108" s="91"/>
+      <c r="D108" s="91"/>
+      <c r="E108" s="91"/>
+      <c r="F108" s="91"/>
+      <c r="G108" s="91"/>
+      <c r="H108" s="91"/>
+      <c r="I108" s="91"/>
+      <c r="J108" s="91"/>
+      <c r="K108" s="91"/>
+      <c r="L108" s="91"/>
+      <c r="M108" s="91"/>
+      <c r="N108" s="91"/>
+      <c r="O108" s="91"/>
+      <c r="P108" s="91"/>
+      <c r="Q108" s="91"/>
+      <c r="R108" s="91"/>
+      <c r="S108" s="91"/>
+      <c r="T108" s="91"/>
+      <c r="U108" s="91"/>
+      <c r="V108" s="91"/>
+      <c r="W108" s="91"/>
+      <c r="X108" s="91"/>
+    </row>
+    <row r="109" spans="2:24" s="60" customFormat="1" ht="15.4">
+      <c r="B109" s="91" t="s">
+        <v>39</v>
+      </c>
+      <c r="C109" s="92">
+        <v>0</v>
+      </c>
+      <c r="D109" s="92">
+        <f>D92</f>
+        <v>0</v>
+      </c>
+      <c r="E109" s="92">
+        <f>D109+E93</f>
+        <v>0</v>
+      </c>
+      <c r="F109" s="92">
+        <f>E109+F93</f>
+        <v>0</v>
+      </c>
+      <c r="G109" s="92">
+        <f t="shared" ref="G109:W109" si="17">F109+G93</f>
+        <v>0</v>
+      </c>
+      <c r="H109" s="92">
         <f t="shared" si="17"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G90" s="107" t="e">
+        <v>0</v>
+      </c>
+      <c r="I109" s="92">
         <f t="shared" si="17"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H90" s="107" t="e">
+        <v>0</v>
+      </c>
+      <c r="J109" s="92">
         <f t="shared" si="17"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I90" s="107" t="e">
+        <v>0</v>
+      </c>
+      <c r="K109" s="92">
         <f t="shared" si="17"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J90" s="107" t="e">
+        <v>0</v>
+      </c>
+      <c r="L109" s="92">
         <f t="shared" si="17"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K90" s="107" t="e">
+        <v>0</v>
+      </c>
+      <c r="M109" s="92">
         <f t="shared" si="17"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L90" s="107" t="e">
+        <v>0</v>
+      </c>
+      <c r="N109" s="92">
         <f t="shared" si="17"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M90" s="107" t="e">
+        <v>0</v>
+      </c>
+      <c r="O109" s="92">
         <f t="shared" si="17"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N90" s="107" t="e">
+        <v>0</v>
+      </c>
+      <c r="P109" s="92">
         <f t="shared" si="17"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O90" s="107" t="e">
+        <v>0</v>
+      </c>
+      <c r="Q109" s="92">
         <f t="shared" si="17"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P90" s="107" t="e">
+        <v>0</v>
+      </c>
+      <c r="R109" s="92">
         <f t="shared" si="17"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q90" s="107" t="e">
+        <v>0</v>
+      </c>
+      <c r="S109" s="92">
         <f t="shared" si="17"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R90" s="107" t="e">
+        <v>0</v>
+      </c>
+      <c r="T109" s="92">
         <f t="shared" si="17"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S90" s="107" t="e">
+        <v>0</v>
+      </c>
+      <c r="U109" s="92">
         <f t="shared" si="17"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T90" s="107" t="e">
+        <v>0</v>
+      </c>
+      <c r="V109" s="92">
         <f t="shared" si="17"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U90" s="107" t="e">
+        <v>0</v>
+      </c>
+      <c r="W109" s="92">
         <f t="shared" si="17"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V90" s="107" t="e">
-        <f t="shared" si="17"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W90" s="107" t="e">
-        <f t="shared" si="17"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X90" s="106"/>
-      <c r="Y90" s="106"/>
-    </row>
-    <row r="91" spans="2:25" s="60" customFormat="1">
-      <c r="B91" s="106" t="s">
-        <v>29</v>
-      </c>
-      <c r="C91" s="106"/>
-      <c r="D91" s="121" t="e">
-        <f>-D72</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E91" s="121" t="e">
-        <f t="shared" ref="E91:W91" si="18">-E72</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F91" s="121" t="e">
-        <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G91" s="121" t="e">
-        <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H91" s="121" t="e">
-        <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I91" s="121" t="e">
-        <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J91" s="121" t="e">
-        <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K91" s="121" t="e">
-        <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L91" s="121" t="e">
-        <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M91" s="121" t="e">
-        <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N91" s="121" t="e">
-        <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O91" s="121" t="e">
-        <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P91" s="121" t="e">
-        <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q91" s="121" t="e">
-        <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R91" s="121" t="e">
-        <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S91" s="121" t="e">
-        <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T91" s="121" t="e">
-        <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U91" s="121" t="e">
-        <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V91" s="121" t="e">
-        <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W91" s="121" t="e">
-        <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X91" s="86"/>
-    </row>
-    <row r="92" spans="2:25" s="60" customFormat="1">
-      <c r="B92" s="106" t="s">
-        <v>30</v>
-      </c>
-      <c r="C92" s="106"/>
-      <c r="D92" s="108" t="e">
-        <f>SUM(D90:D91)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E92" s="108" t="e">
-        <f t="shared" ref="E92:W92" si="19">SUM(E90:E91)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F92" s="108" t="e">
-        <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G92" s="108" t="e">
-        <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H92" s="108" t="e">
-        <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I92" s="108" t="e">
-        <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J92" s="108" t="e">
-        <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K92" s="108" t="e">
-        <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L92" s="108" t="e">
-        <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M92" s="108" t="e">
-        <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N92" s="108" t="e">
-        <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O92" s="108" t="e">
-        <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P92" s="108" t="e">
-        <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q92" s="108" t="e">
-        <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R92" s="108" t="e">
-        <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S92" s="108" t="e">
-        <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T92" s="108" t="e">
-        <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U92" s="108" t="e">
-        <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V92" s="108" t="e">
-        <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W92" s="108" t="e">
-        <f t="shared" si="19"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X92" s="109"/>
-    </row>
-    <row r="93" spans="2:25" s="60" customFormat="1">
-      <c r="B93" s="106"/>
-      <c r="C93" s="106"/>
-      <c r="D93" s="106"/>
-      <c r="E93" s="106"/>
-      <c r="F93" s="110"/>
-      <c r="G93" s="110"/>
-      <c r="H93" s="110"/>
-      <c r="I93" s="110"/>
-      <c r="J93" s="110"/>
-      <c r="K93" s="110"/>
-      <c r="L93" s="110"/>
-      <c r="M93" s="110"/>
-      <c r="N93" s="110"/>
-      <c r="O93" s="110"/>
-      <c r="P93" s="110"/>
-      <c r="Q93" s="110"/>
-      <c r="R93" s="110"/>
-      <c r="S93" s="110"/>
-      <c r="T93" s="110"/>
-      <c r="U93" s="110"/>
-      <c r="V93" s="110"/>
-      <c r="W93" s="110"/>
-      <c r="X93" s="111"/>
-    </row>
-    <row r="94" spans="2:25" s="60" customFormat="1">
-      <c r="B94" s="112" t="s">
-        <v>31</v>
-      </c>
-      <c r="C94" s="113"/>
-      <c r="D94" s="114">
-        <f>C44</f>
-        <v>0</v>
-      </c>
-      <c r="E94" s="113"/>
-      <c r="F94" s="113"/>
-      <c r="G94" s="113"/>
-      <c r="H94" s="113"/>
-      <c r="I94" s="113"/>
-      <c r="J94" s="113"/>
-      <c r="K94" s="113"/>
-      <c r="L94" s="113"/>
-      <c r="M94" s="113"/>
-      <c r="N94" s="113"/>
-      <c r="O94" s="113"/>
-      <c r="P94" s="113"/>
-      <c r="Q94" s="113"/>
-      <c r="R94" s="113"/>
-      <c r="S94" s="113"/>
-      <c r="T94" s="113"/>
-      <c r="U94" s="113"/>
-      <c r="V94" s="113"/>
-      <c r="W94" s="113"/>
-      <c r="X94" s="86"/>
-    </row>
-    <row r="95" spans="2:25" s="60" customFormat="1">
-      <c r="B95" s="106"/>
-      <c r="C95" s="106"/>
-      <c r="D95" s="106"/>
-      <c r="E95" s="106"/>
-      <c r="F95" s="110"/>
-      <c r="G95" s="110"/>
-      <c r="H95" s="110"/>
-      <c r="I95" s="110"/>
-      <c r="J95" s="110"/>
-      <c r="K95" s="110"/>
-      <c r="L95" s="110"/>
-      <c r="M95" s="110"/>
-      <c r="N95" s="110"/>
-      <c r="O95" s="110"/>
-      <c r="P95" s="110"/>
-      <c r="Q95" s="110"/>
-      <c r="R95" s="110"/>
-      <c r="S95" s="110"/>
-      <c r="T95" s="110"/>
-      <c r="U95" s="110"/>
-      <c r="V95" s="110"/>
-      <c r="W95" s="110"/>
-      <c r="X95" s="111"/>
-    </row>
-    <row r="96" spans="2:25" s="60" customFormat="1">
-      <c r="B96" s="106"/>
-      <c r="C96" s="106"/>
-      <c r="D96" s="106"/>
-      <c r="E96" s="106"/>
-      <c r="F96" s="110"/>
-      <c r="G96" s="110"/>
-      <c r="H96" s="110"/>
-      <c r="I96" s="110"/>
-      <c r="J96" s="110"/>
-      <c r="K96" s="110"/>
-      <c r="L96" s="110"/>
-      <c r="M96" s="110"/>
-      <c r="N96" s="110"/>
-      <c r="O96" s="110"/>
-      <c r="P96" s="110"/>
-      <c r="Q96" s="110"/>
-      <c r="R96" s="110"/>
-      <c r="S96" s="110"/>
-      <c r="T96" s="110"/>
-      <c r="U96" s="110"/>
-      <c r="V96" s="110"/>
-      <c r="W96" s="110"/>
-      <c r="X96" s="111"/>
-    </row>
-    <row r="97" spans="2:24" s="60" customFormat="1">
-      <c r="B97" s="112" t="s">
-        <v>32</v>
-      </c>
-      <c r="C97" s="113"/>
-      <c r="D97" s="114">
-        <f>-D94*D31</f>
-        <v>0</v>
-      </c>
-      <c r="E97" s="113"/>
-      <c r="F97" s="113"/>
-      <c r="G97" s="113"/>
-      <c r="H97" s="113"/>
-      <c r="I97" s="113"/>
-      <c r="J97" s="113"/>
-      <c r="K97" s="113"/>
-      <c r="L97" s="113"/>
-      <c r="M97" s="113"/>
-      <c r="N97" s="113"/>
-      <c r="O97" s="113"/>
-      <c r="P97" s="113"/>
-      <c r="Q97" s="113"/>
-      <c r="R97" s="113"/>
-      <c r="S97" s="113"/>
-      <c r="T97" s="113"/>
-      <c r="U97" s="113"/>
-      <c r="V97" s="113"/>
-      <c r="W97" s="113"/>
-      <c r="X97" s="111"/>
-    </row>
-    <row r="98" spans="2:24" s="60" customFormat="1">
-      <c r="B98" s="106" t="s">
-        <v>33</v>
-      </c>
-      <c r="C98" s="106"/>
-      <c r="D98" s="106"/>
-      <c r="E98" s="106"/>
-      <c r="F98" s="106"/>
-      <c r="G98" s="106"/>
-      <c r="H98" s="106"/>
-      <c r="I98" s="106"/>
-      <c r="J98" s="106"/>
-      <c r="K98" s="106"/>
-      <c r="L98" s="106"/>
-      <c r="M98" s="106"/>
-      <c r="N98" s="106"/>
-      <c r="O98" s="106"/>
-      <c r="P98" s="106"/>
-      <c r="Q98" s="106"/>
-      <c r="R98" s="106"/>
-      <c r="S98" s="106"/>
-      <c r="T98" s="110"/>
-      <c r="U98" s="110"/>
-      <c r="V98" s="110"/>
-      <c r="W98" s="110"/>
-      <c r="X98" s="86"/>
-    </row>
-    <row r="99" spans="2:24" s="60" customFormat="1">
-      <c r="B99" s="106" t="s">
-        <v>34</v>
-      </c>
-      <c r="C99" s="110"/>
-      <c r="D99" s="107">
-        <f>-D94*(1-D31)</f>
-        <v>0</v>
-      </c>
-      <c r="E99" s="110"/>
-      <c r="F99" s="110"/>
-      <c r="G99" s="110"/>
-      <c r="H99" s="110"/>
-      <c r="I99" s="110"/>
-      <c r="J99" s="110"/>
-      <c r="K99" s="110"/>
-      <c r="L99" s="110"/>
-      <c r="M99" s="110"/>
-      <c r="N99" s="110"/>
-      <c r="O99" s="110"/>
-      <c r="P99" s="110"/>
-      <c r="Q99" s="110"/>
-      <c r="R99" s="110"/>
-      <c r="S99" s="110"/>
-      <c r="T99" s="110"/>
-      <c r="U99" s="110"/>
-      <c r="V99" s="110"/>
-      <c r="W99" s="110"/>
-      <c r="X99" s="109"/>
-    </row>
-    <row r="100" spans="2:24" s="60" customFormat="1">
-      <c r="B100" s="106" t="s">
-        <v>35</v>
-      </c>
-      <c r="C100" s="110"/>
-      <c r="D100" s="110"/>
-      <c r="E100" s="144" t="e">
-        <f>-D90*$D$33</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F100" s="144" t="e">
-        <f t="shared" ref="F100:W100" si="20">-E90*$D$33</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G100" s="144" t="e">
-        <f t="shared" si="20"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H100" s="144" t="e">
-        <f t="shared" si="20"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I100" s="144" t="e">
-        <f t="shared" si="20"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J100" s="144" t="e">
-        <f t="shared" si="20"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K100" s="144" t="e">
-        <f t="shared" si="20"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L100" s="144" t="e">
-        <f t="shared" si="20"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M100" s="144" t="e">
-        <f t="shared" si="20"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N100" s="144" t="e">
-        <f t="shared" si="20"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O100" s="144" t="e">
-        <f t="shared" si="20"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P100" s="144" t="e">
-        <f t="shared" si="20"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q100" s="144" t="e">
-        <f t="shared" si="20"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R100" s="144" t="e">
-        <f t="shared" si="20"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S100" s="144" t="e">
-        <f t="shared" si="20"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T100" s="144" t="e">
-        <f t="shared" si="20"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U100" s="144" t="e">
-        <f t="shared" si="20"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V100" s="144" t="e">
-        <f t="shared" si="20"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W100" s="144" t="e">
-        <f t="shared" si="20"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X100" s="145" t="e">
-        <f>-W90</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="101" spans="2:24" s="60" customFormat="1">
-      <c r="B101" s="115" t="s">
-        <v>36</v>
-      </c>
-      <c r="C101" s="116"/>
-      <c r="D101" s="116"/>
-      <c r="E101" s="146"/>
-      <c r="F101" s="146"/>
-      <c r="G101" s="146"/>
-      <c r="H101" s="146"/>
-      <c r="I101" s="146"/>
-      <c r="J101" s="146"/>
-      <c r="K101" s="146"/>
-      <c r="L101" s="146"/>
-      <c r="M101" s="146"/>
-      <c r="N101" s="146"/>
-      <c r="O101" s="146"/>
-      <c r="P101" s="146"/>
-      <c r="Q101" s="146"/>
-      <c r="R101" s="147"/>
-      <c r="S101" s="147"/>
-      <c r="T101" s="147"/>
-      <c r="U101" s="147"/>
-      <c r="V101" s="146"/>
-      <c r="W101" s="146"/>
-      <c r="X101" s="145" t="e">
-        <f>-W106-X100</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="102" spans="2:24" s="60" customFormat="1">
-      <c r="B102" s="110"/>
-      <c r="C102" s="110"/>
-      <c r="D102" s="110"/>
-      <c r="E102" s="110"/>
-      <c r="F102" s="110"/>
-      <c r="G102" s="110"/>
-      <c r="H102" s="110"/>
-      <c r="I102" s="110"/>
-      <c r="J102" s="110"/>
-      <c r="K102" s="110"/>
-      <c r="L102" s="110"/>
-      <c r="M102" s="110"/>
-      <c r="N102" s="110"/>
-      <c r="O102" s="110"/>
-      <c r="P102" s="110"/>
-      <c r="Q102" s="110"/>
-      <c r="R102" s="110"/>
-      <c r="S102" s="110"/>
-      <c r="T102" s="110"/>
-      <c r="U102" s="110"/>
-      <c r="V102" s="110"/>
-      <c r="W102" s="110"/>
-      <c r="X102" s="109"/>
-    </row>
-    <row r="103" spans="2:24" s="60" customFormat="1">
-      <c r="B103" s="110"/>
-      <c r="C103" s="110"/>
-      <c r="D103" s="110"/>
-      <c r="E103" s="110"/>
-      <c r="F103" s="110"/>
-      <c r="G103" s="110"/>
-      <c r="H103" s="110"/>
-      <c r="I103" s="110"/>
-      <c r="J103" s="110"/>
-      <c r="K103" s="110"/>
-      <c r="L103" s="110"/>
-      <c r="M103" s="110"/>
-      <c r="N103" s="110"/>
-      <c r="O103" s="110"/>
-      <c r="P103" s="110"/>
-      <c r="Q103" s="110"/>
-      <c r="R103" s="110"/>
-      <c r="S103" s="110"/>
-      <c r="T103" s="110"/>
-      <c r="U103" s="110"/>
-      <c r="V103" s="110"/>
-      <c r="W103" s="110"/>
-      <c r="X103" s="109"/>
-    </row>
-    <row r="104" spans="2:24" s="60" customFormat="1" ht="16.5">
-      <c r="B104" s="106" t="s">
-        <v>37</v>
-      </c>
-      <c r="C104" s="117">
-        <v>0</v>
-      </c>
-      <c r="D104" s="107" t="e">
-        <f>SUM(D92:D101)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E104" s="107" t="e">
-        <f t="shared" ref="E104:W104" si="21">SUM(E92:E101)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F104" s="107" t="e">
-        <f t="shared" si="21"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G104" s="107" t="e">
-        <f t="shared" si="21"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H104" s="107" t="e">
-        <f t="shared" si="21"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I104" s="107" t="e">
-        <f t="shared" si="21"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J104" s="107" t="e">
-        <f t="shared" si="21"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K104" s="107" t="e">
-        <f t="shared" si="21"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L104" s="107" t="e">
-        <f t="shared" si="21"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M104" s="107" t="e">
-        <f t="shared" si="21"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N104" s="107" t="e">
-        <f t="shared" si="21"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O104" s="107" t="e">
-        <f t="shared" si="21"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P104" s="107" t="e">
-        <f t="shared" si="21"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q104" s="107" t="e">
-        <f t="shared" si="21"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R104" s="107" t="e">
-        <f t="shared" si="21"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S104" s="107" t="e">
-        <f t="shared" si="21"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T104" s="107" t="e">
-        <f t="shared" si="21"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U104" s="107" t="e">
-        <f t="shared" si="21"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V104" s="107" t="e">
-        <f t="shared" si="21"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W104" s="107" t="e">
-        <f t="shared" si="21"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X104" s="109"/>
-    </row>
-    <row r="105" spans="2:24" s="60" customFormat="1">
-      <c r="B105" s="106" t="s">
-        <v>38</v>
-      </c>
-      <c r="C105" s="107">
-        <v>0</v>
-      </c>
-      <c r="D105" s="107">
-        <f>C106</f>
-        <v>0</v>
-      </c>
-      <c r="E105" s="107" t="e">
-        <f>D106</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F105" s="107" t="e">
-        <f>E106</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G105" s="107" t="e">
-        <f t="shared" ref="G105:W105" si="22">F106</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H105" s="107" t="e">
-        <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I105" s="107" t="e">
-        <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J105" s="107" t="e">
-        <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K105" s="107" t="e">
-        <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L105" s="107" t="e">
-        <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M105" s="107" t="e">
-        <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N105" s="107" t="e">
-        <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O105" s="107" t="e">
-        <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P105" s="107" t="e">
-        <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q105" s="107" t="e">
-        <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R105" s="107" t="e">
-        <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S105" s="107" t="e">
-        <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T105" s="107" t="e">
-        <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U105" s="107" t="e">
-        <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V105" s="107" t="e">
-        <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W105" s="107" t="e">
-        <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X105" s="111"/>
-    </row>
-    <row r="106" spans="2:24" s="60" customFormat="1">
-      <c r="B106" s="106" t="s">
-        <v>39</v>
-      </c>
-      <c r="C106" s="107">
-        <v>0</v>
-      </c>
-      <c r="D106" s="107" t="e">
-        <f>D104+D105</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E106" s="107" t="e">
-        <f>E104+E105</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F106" s="107" t="e">
-        <f t="shared" ref="F106:W106" si="23">F104+F105</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G106" s="107" t="e">
-        <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H106" s="107" t="e">
-        <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I106" s="107" t="e">
-        <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J106" s="107" t="e">
-        <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K106" s="107" t="e">
-        <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L106" s="107" t="e">
-        <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M106" s="107" t="e">
-        <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N106" s="107" t="e">
-        <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O106" s="107" t="e">
-        <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P106" s="107" t="e">
-        <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q106" s="107" t="e">
-        <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R106" s="107" t="e">
-        <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S106" s="107" t="e">
-        <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T106" s="107" t="e">
-        <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U106" s="107" t="e">
-        <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V106" s="107" t="e">
-        <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W106" s="107" t="e">
-        <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X106" s="111"/>
-    </row>
-    <row r="107" spans="2:24" s="60" customFormat="1">
-      <c r="B107" s="106"/>
-      <c r="C107" s="106"/>
-      <c r="D107" s="106"/>
-      <c r="E107" s="106"/>
-      <c r="F107" s="106"/>
-      <c r="G107" s="106"/>
-      <c r="H107" s="106"/>
-      <c r="I107" s="106"/>
-      <c r="J107" s="106"/>
-      <c r="K107" s="106"/>
-      <c r="L107" s="106"/>
-      <c r="M107" s="106"/>
-      <c r="N107" s="106"/>
-      <c r="O107" s="106"/>
-      <c r="P107" s="106"/>
-      <c r="Q107" s="106"/>
-      <c r="R107" s="106"/>
-      <c r="S107" s="106"/>
-      <c r="T107" s="106"/>
-      <c r="U107" s="106"/>
-      <c r="V107" s="106"/>
-      <c r="W107" s="106"/>
-      <c r="X107" s="106"/>
-    </row>
-    <row r="108" spans="2:24" s="60" customFormat="1">
-      <c r="B108" s="106"/>
-      <c r="C108" s="106"/>
-      <c r="D108" s="106"/>
-      <c r="E108" s="106"/>
-      <c r="F108" s="110"/>
-      <c r="G108" s="106"/>
-      <c r="H108" s="106"/>
-      <c r="I108" s="106"/>
-      <c r="J108" s="106"/>
-      <c r="K108" s="106"/>
-      <c r="L108" s="106"/>
-      <c r="M108" s="106"/>
-      <c r="N108" s="106"/>
-      <c r="O108" s="106"/>
-      <c r="P108" s="106"/>
-      <c r="Q108" s="106"/>
-      <c r="R108" s="106"/>
-      <c r="S108" s="106"/>
-      <c r="T108" s="106"/>
-      <c r="U108" s="106"/>
-      <c r="V108" s="106"/>
-      <c r="W108" s="106"/>
-      <c r="X108" s="106"/>
-    </row>
-    <row r="109" spans="2:24" s="60" customFormat="1">
-      <c r="B109" s="118" t="s">
-        <v>40</v>
-      </c>
-      <c r="C109" s="119"/>
-      <c r="D109" s="120">
-        <f>-D99</f>
-        <v>0</v>
-      </c>
-      <c r="E109" s="108" t="e">
-        <f>-E100-E101</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F109" s="108" t="e">
-        <f t="shared" ref="F109:X109" si="24">-F100-F101</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G109" s="108" t="e">
-        <f t="shared" si="24"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H109" s="108" t="e">
-        <f t="shared" si="24"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I109" s="108" t="e">
-        <f t="shared" si="24"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J109" s="108" t="e">
-        <f t="shared" si="24"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K109" s="108" t="e">
-        <f t="shared" si="24"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L109" s="108" t="e">
-        <f t="shared" si="24"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M109" s="108" t="e">
-        <f t="shared" si="24"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N109" s="108" t="e">
-        <f t="shared" si="24"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O109" s="108" t="e">
-        <f t="shared" si="24"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P109" s="108" t="e">
-        <f t="shared" si="24"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q109" s="108" t="e">
-        <f t="shared" si="24"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R109" s="108" t="e">
-        <f t="shared" si="24"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S109" s="108" t="e">
-        <f t="shared" si="24"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T109" s="108" t="e">
-        <f t="shared" si="24"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U109" s="108" t="e">
-        <f t="shared" si="24"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V109" s="108" t="e">
-        <f t="shared" si="24"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W109" s="108" t="e">
-        <f t="shared" si="24"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X109" s="108" t="e">
-        <f t="shared" si="24"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="110" spans="2:24" s="60" customFormat="1">
-      <c r="B110" s="106" t="s">
-        <v>41</v>
-      </c>
-      <c r="C110" s="123" t="e">
-        <f>IRR(D109:X109)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D110" s="110"/>
-      <c r="E110" s="110"/>
-      <c r="F110" s="106"/>
-      <c r="G110" s="106"/>
-      <c r="H110" s="106"/>
-      <c r="I110" s="106"/>
-      <c r="J110" s="106"/>
-      <c r="K110" s="106"/>
-      <c r="L110" s="106"/>
-      <c r="M110" s="106"/>
-      <c r="N110" s="106"/>
-      <c r="O110" s="106"/>
-      <c r="P110" s="106"/>
-      <c r="Q110" s="106"/>
-      <c r="R110" s="106"/>
-      <c r="S110" s="106"/>
-      <c r="T110" s="106"/>
-      <c r="U110" s="106"/>
-      <c r="V110" s="106"/>
-      <c r="W110" s="106"/>
-      <c r="X110" s="106"/>
-    </row>
-    <row r="111" spans="2:24" s="60" customFormat="1">
-      <c r="B111" s="118" t="s">
-        <v>42</v>
-      </c>
-      <c r="C111" s="119"/>
-      <c r="D111" s="120" t="e">
-        <f>D90-D99</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E111" s="108" t="e">
-        <f>E90</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F111" s="108" t="e">
-        <f>F90-F101</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G111" s="108" t="e">
-        <f t="shared" ref="G111:W111" si="25">G90-G101</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H111" s="108" t="e">
-        <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I111" s="108" t="e">
-        <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J111" s="108" t="e">
-        <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K111" s="108" t="e">
-        <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L111" s="108" t="e">
-        <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M111" s="108" t="e">
-        <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N111" s="108" t="e">
-        <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O111" s="108" t="e">
-        <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P111" s="108" t="e">
-        <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q111" s="108" t="e">
-        <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R111" s="108" t="e">
-        <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S111" s="108" t="e">
-        <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T111" s="108" t="e">
-        <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U111" s="108" t="e">
-        <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V111" s="108" t="e">
-        <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W111" s="108" t="e">
-        <f t="shared" si="25"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X111" s="86"/>
-    </row>
-    <row r="112" spans="2:24" s="60" customFormat="1">
-      <c r="B112" s="118" t="s">
-        <v>43</v>
-      </c>
-      <c r="C112" s="122" t="e">
-        <f>IRR(D111:W111)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D112" s="110"/>
-      <c r="E112" s="110"/>
-      <c r="F112" s="106"/>
-      <c r="G112" s="106"/>
-      <c r="H112" s="106"/>
-      <c r="I112" s="106"/>
-      <c r="J112" s="106"/>
-      <c r="K112" s="106"/>
-      <c r="L112" s="106"/>
-      <c r="M112" s="106"/>
-      <c r="N112" s="106"/>
-      <c r="O112" s="106"/>
-      <c r="P112" s="106"/>
-      <c r="Q112" s="106"/>
-      <c r="R112" s="106"/>
-      <c r="S112" s="106"/>
-      <c r="T112" s="106"/>
-      <c r="U112" s="106"/>
-      <c r="V112" s="106"/>
-      <c r="W112" s="106"/>
-      <c r="X112" s="106"/>
-    </row>
-    <row r="113" spans="2:24" s="60" customFormat="1">
-      <c r="B113" s="106"/>
-      <c r="C113" s="106"/>
-      <c r="D113" s="106"/>
-      <c r="E113" s="106"/>
-      <c r="F113" s="106"/>
-      <c r="G113" s="106"/>
-      <c r="H113" s="106"/>
-      <c r="I113" s="106"/>
-      <c r="J113" s="106"/>
-      <c r="K113" s="106"/>
-      <c r="L113" s="106"/>
-      <c r="M113" s="106"/>
-      <c r="N113" s="106"/>
-      <c r="O113" s="106"/>
-      <c r="P113" s="106"/>
-      <c r="Q113" s="106"/>
-      <c r="R113" s="106"/>
-      <c r="S113" s="106"/>
-      <c r="T113" s="106"/>
-      <c r="U113" s="106"/>
-      <c r="V113" s="106"/>
-      <c r="W113" s="106"/>
-      <c r="X113" s="106"/>
-    </row>
-    <row r="114" spans="2:24" s="60" customFormat="1">
-      <c r="B114" s="106" t="s">
-        <v>44</v>
-      </c>
-      <c r="C114" s="107">
-        <v>0</v>
-      </c>
-      <c r="D114" s="107">
-        <f>D97</f>
-        <v>0</v>
-      </c>
-      <c r="E114" s="107">
-        <f>D114+E98</f>
-        <v>0</v>
-      </c>
-      <c r="F114" s="107">
-        <f>E114+F98</f>
-        <v>0</v>
-      </c>
-      <c r="G114" s="107">
-        <f t="shared" ref="G114:W114" si="26">F114+G98</f>
-        <v>0</v>
-      </c>
-      <c r="H114" s="107">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="I114" s="107">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="J114" s="107">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="K114" s="107">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="L114" s="107">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="M114" s="107">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="N114" s="107">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="O114" s="107">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="P114" s="107">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="Q114" s="107">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="R114" s="107">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="S114" s="107">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="T114" s="107">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="U114" s="107">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="V114" s="107">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="W114" s="107">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="X114" s="110"/>
-    </row>
-    <row r="116" spans="2:24">
-      <c r="B116" s="41"/>
-    </row>
-    <row r="117" spans="2:24" ht="16.5">
-      <c r="G117" s="33"/>
+        <v>0</v>
+      </c>
+      <c r="X109" s="95"/>
+    </row>
+    <row r="111" spans="2:24">
+      <c r="B111" s="41"/>
+    </row>
+    <row r="112" spans="2:24" ht="16.149999999999999">
+      <c r="G112" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="B10:B13"/>
+    <mergeCell ref="E10:E13"/>
     <mergeCell ref="B14:E14"/>
     <mergeCell ref="B16:B18"/>
     <mergeCell ref="E16:E18"/>
     <mergeCell ref="B19:B21"/>
     <mergeCell ref="B29:D29"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="B10:B13"/>
-    <mergeCell ref="E10:E13"/>
   </mergeCells>
-  <phoneticPr fontId="26" type="noConversion"/>
+  <phoneticPr fontId="24" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>